--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -797,7 +797,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>VP Arc (USA)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
@@ -811,30 +811,51 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>8 VP arc events</t>
+          <t>8 VP arc events — Ualani + elected VP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>CA Events</t>
+          <t>PM Arc (CA)</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>11 alliance arc · 24 CA protector events (8 protectors × 3)</t>
+          <t>9 CA President arc events — Jessica + Mark Penoit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>CA Events</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>CA protectors (8×3) · alliance arc · collapse events · USA-CA alliance (CA side)</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6836,48 +6857,108 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>CANADIAN PROTECTORS  (8 protectors × 3 events each)</t>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>USA Alliance Arc</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>USA_CALL_01</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>A DISPATCH FROM WASHINGTON — THE AMERICANS WANT TO TALK</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Root (turn 8+, req: uk_buildup_known)</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Sets usa_contact flag; gates USA_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>BTN1: Hear them out (→ USA_SUMMIT_01) · BTN2: Decline (sets usa_rejected → CA_ALONE_01)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>CA PROTECTOR — LE WENDIGO</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>USA Alliance Arc</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>USA_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>THE OTTAWA SUMMIT — JESSICA CLEAR-WATER MEETS THE AMERICAN DELEGATION</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Branch (req: usa_contact, turn 13+)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Sets usa_summit_complete flag</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>BTN1: Sign the accord (→ USA_ALLIANCE_SIGNED) · BTN2: Walk away (sets usa_rejected)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>CA Protector — Le Wendigo</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_SUMMON</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>LE WENDIGO WAKES IN THE LAURENTIAN FOREST</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Fires when Laurentian region contested</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Summon/tame/agreement chain; grants Le Wendigo's Hunger mil mod</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>USA Alliance Arc</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>USA_ALLIANCE_SIGNED</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>THE DOMINION-REPUBLIC ACCORD IS SIGNED</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Branch (req: usa_summit_complete)</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Sets ca_allied flag; mirrors CAN_ALLIANCE_SIGNED from USA side</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Narrative resolution; alliance milestone event</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -6889,32 +6970,32 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Le Wendigo</t>
+          <t>USA Alliance Arc</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_01_TAME</t>
+          <t>CA_ALONE_01</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>THE WENDIGO RECEDES FROM THE HARVEST CORRIDOR</t>
+          <t>CANADA STANDS ALONE — THE DOMINION DECLINES THE AMERICAN OFFER</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Branch (req: usa_rejected flag)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Req: PROT_01_SUMMON</t>
+          <t>Canada fights without USA alliance</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_01_AGREE; negotiation event</t>
+          <t>Narrative event; opens solo-play diplomatic tree</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -6924,63 +7005,33 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>CA Protector — Le Wendigo</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_AGREE</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Req: CA_PROT_01_TAME</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Protector ally secured; mil mod applied</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>CANADIAN PROTECTORS  (8 protectors × 3 events each)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LE LOUP-GAROU</t>
+          <t>CA PROTECTOR — LE WENDIGO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Le Loup-Garou</t>
+          <t>CA Protector — Le Wendigo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_02_SUMMON</t>
+          <t>CA_PROT_01_SUMMON</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU RUNS THE RIVER ROAD — RIVIÈRE-DU-LOUP QUARANTINED</t>
+          <t>LE WENDIGO WAKES IN THE LAURENTIAN FOREST</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -6990,12 +7041,12 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Fires near Rivière-du-Loup tile</t>
+          <t>Fires when Laurentian region contested</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame/agreement chain; grants Loup-Garou's Frenzy mil mod</t>
+          <t>Summon/tame/agreement chain; grants Le Wendigo's Hunger mil mod</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -7007,17 +7058,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Le Loup-Garou</t>
+          <t>CA Protector — Le Wendigo</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_02_TAME</t>
+          <t>CA_PROT_01_TAME</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU ALLOWS PASSAGE — THE RIVER ROAD REOPENS</t>
+          <t>THE WENDIGO RECEDES FROM THE HARVEST CORRIDOR</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -7027,12 +7078,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_02_SUMMON</t>
+          <t>Req: PROT_01_SUMMON</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_02_AGREE</t>
+          <t>→ CA_PROT_01_AGREE; negotiation event</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -7044,17 +7095,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Le Loup-Garou</t>
+          <t>CA Protector — Le Wendigo</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE</t>
+          <t>CA_PROT_01_AGREE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -7064,12 +7115,12 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_02_TAME</t>
+          <t>Req: CA_PROT_01_TAME</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Protector ally secured</t>
+          <t>Protector ally secured; mil mod applied</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -7081,24 +7132,24 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LES FEUX FOLLETS</t>
+          <t>CA PROTECTOR — LE LOUP-GAROU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Les Feux Follets</t>
+          <t>CA Protector — Le Loup-Garou</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_03_SUMMON</t>
+          <t>CA_PROT_02_SUMMON</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS RISE OVER THE SAINT JOHN MARSHES — NAVIGATION DISRUPTED</t>
+          <t>LE LOUP-GAROU RUNS THE RIVER ROAD — RIVIÈRE-DU-LOUP QUARANTINED</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -7108,12 +7159,12 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Fires near Saint John marshes</t>
+          <t>Fires near Rivière-du-Loup tile</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants Feux Follets' Misdirection</t>
+          <t>Summon/tame/agreement chain; grants Loup-Garou's Frenzy mil mod</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -7125,17 +7176,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Les Feux Follets</t>
+          <t>CA Protector — Le Loup-Garou</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_03_TAME</t>
+          <t>CA_PROT_02_TAME</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS QUIET — MALISEET PROTOCOLS ESTABLISHED</t>
+          <t>LE LOUP-GAROU ALLOWS PASSAGE — THE RIVER ROAD REOPENS</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -7145,12 +7196,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_03_SUMMON</t>
+          <t>Req: CA_PROT_02_SUMMON</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_03_AGREE; cultural protocol required</t>
+          <t>→ CA_PROT_02_AGREE</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -7162,17 +7213,17 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Les Feux Follets</t>
+          <t>CA Protector — Le Loup-Garou</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE</t>
+          <t>CA_PROT_02_AGREE</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -7182,7 +7233,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_03_TAME</t>
+          <t>Req: CA_PROT_02_TAME</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -7199,24 +7250,24 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — MISHEPESHU</t>
+          <t>CA PROTECTOR — LES FEUX FOLLETS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Mishepeshu</t>
+          <t>CA Protector — Les Feux Follets</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_04_SUMMON</t>
+          <t>CA_PROT_03_SUMMON</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>MISHEPESHU STIRS BENEATH LAKE SIMCOE — CROSSINGS CONTESTED</t>
+          <t>LES FEUX FOLLETS RISE OVER THE SAINT JOHN MARSHES — NAVIGATION DISRUPTED</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -7226,12 +7277,12 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Fires near Lake Simcoe</t>
+          <t>Fires near Saint John marshes</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants Mishepeshu's Depths</t>
+          <t>Summon/tame chain; grants Feux Follets' Misdirection</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -7243,17 +7294,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Mishepeshu</t>
+          <t>CA Protector — Les Feux Follets</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_04_TAME</t>
+          <t>CA_PROT_03_TAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>MISHEPESHU WITHDRAWS FROM THE CROSSING LANES</t>
+          <t>LES FEUX FOLLETS QUIET — MALISEET PROTOCOLS ESTABLISHED</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -7263,12 +7314,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_04_SUMMON</t>
+          <t>Req: CA_PROT_03_SUMMON</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_04_AGREE</t>
+          <t>→ CA_PROT_03_AGREE; cultural protocol required</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -7280,17 +7331,17 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Mishepeshu</t>
+          <t>CA Protector — Les Feux Follets</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE</t>
+          <t>CA_PROT_03_AGREE</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -7300,7 +7351,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_04_TAME</t>
+          <t>Req: CA_PROT_03_TAME</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -7317,24 +7368,24 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LA CORRIVEAU</t>
+          <t>CA PROTECTOR — MISHEPESHU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — La Corriveau</t>
+          <t>CA Protector — Mishepeshu</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_05_SUMMON</t>
+          <t>CA_PROT_04_SUMMON</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU IS FREE — THE IRON CAGE HAS BEEN SWINGING IN TROIS-PISTOLES</t>
+          <t>MISHEPESHU STIRS BENEATH LAKE SIMCOE — CROSSINGS CONTESTED</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -7344,12 +7395,12 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Fires near Trois-Pistoles tile</t>
+          <t>Fires near Lake Simcoe</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants La Corriveau's Cage</t>
+          <t>Summon/tame chain; grants Mishepeshu's Depths</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -7361,17 +7412,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — La Corriveau</t>
+          <t>CA Protector — Mishepeshu</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_05_TAME</t>
+          <t>CA_PROT_04_TAME</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU QUIETS — THE REPUBLIC ACKNOWLEDGES THE VERDICT WAS WRONG</t>
+          <t>MISHEPESHU WITHDRAWS FROM THE CROSSING LANES</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7381,12 +7432,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_05_SUMMON</t>
+          <t>Req: CA_PROT_04_SUMMON</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_05_AGREE; justice acknowledgment required</t>
+          <t>→ CA_PROT_04_AGREE</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -7398,17 +7449,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — La Corriveau</t>
+          <t>CA Protector — Mishepeshu</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE</t>
+          <t>CA_PROT_04_AGREE</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC</t>
+          <t>MISHEPESHU PACT: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -7418,7 +7469,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_05_TAME</t>
+          <t>Req: CA_PROT_04_TAME</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -7435,24 +7486,24 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LE CARCAJOU</t>
+          <t>CA PROTECTOR — LA CORRIVEAU</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Le Carcajou</t>
+          <t>CA Protector — La Corriveau</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_06_SUMMON</t>
+          <t>CA_PROT_05_SUMMON</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>LE CARCAJOU MOVES THROUGH THE MONCTON FOREST — NOTHING STOPS IT</t>
+          <t>LA CORRIVEAU IS FREE — THE IRON CAGE HAS BEEN SWINGING IN TROIS-PISTOLES</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -7462,12 +7513,12 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Fires near Moncton tile</t>
+          <t>Fires near Trois-Pistoles tile</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants Le Carcajou's Tenacity</t>
+          <t>Summon/tame chain; grants La Corriveau's Cage</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -7479,17 +7530,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Le Carcajou</t>
+          <t>CA Protector — La Corriveau</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_06_TAME</t>
+          <t>CA_PROT_05_TAME</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>LE CARCAJOU REDIRECTS — CONTINENTAL LINES EXEMPTED</t>
+          <t>LA CORRIVEAU QUIETS — THE REPUBLIC ACKNOWLEDGES THE VERDICT WAS WRONG</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -7499,12 +7550,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_06_SUMMON</t>
+          <t>Req: CA_PROT_05_SUMMON</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_06_AGREE</t>
+          <t>→ CA_PROT_05_AGREE; justice acknowledgment required</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -7516,17 +7567,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Le Carcajou</t>
+          <t>CA Protector — La Corriveau</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE</t>
+          <t>CA_PROT_05_AGREE</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -7536,7 +7587,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_06_TAME</t>
+          <t>Req: CA_PROT_05_TAME</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -7553,24 +7604,24 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LA CHASSE-GALERIE</t>
+          <t>CA PROTECTOR — LE CARCAJOU</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — La Chasse-Galerie</t>
+          <t>CA Protector — Le Carcajou</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_07_SUMMON</t>
+          <t>CA_PROT_06_SUMMON</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>THE FLYING CANOE RUNS THE OTTAWA RIVER — THREE SIGHTINGS, TWO MISSING PATROLS</t>
+          <t>LE CARCAJOU MOVES THROUGH THE MONCTON FOREST — NOTHING STOPS IT</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -7580,12 +7631,12 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Fires near Ottawa River corridor</t>
+          <t>Fires near Moncton tile</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants La Chasse-Galerie mil mod</t>
+          <t>Summon/tame chain; grants Le Carcajou's Tenacity</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -7597,17 +7648,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — La Chasse-Galerie</t>
+          <t>CA Protector — Le Carcajou</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_07_TAME</t>
+          <t>CA_PROT_06_TAME</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>THE FLYING CANOE ACKNOWLEDGES THE REPUBLIC — OTTAWA CORRIDOR SECURED</t>
+          <t>LE CARCAJOU REDIRECTS — CONTINENTAL LINES EXEMPTED</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -7617,12 +7668,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_07_SUMMON</t>
+          <t>Req: CA_PROT_06_SUMMON</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_07_AGREE</t>
+          <t>→ CA_PROT_06_AGREE</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -7634,17 +7685,17 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — La Chasse-Galerie</t>
+          <t>CA Protector — Le Carcajou</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE</t>
+          <t>CA_PROT_06_AGREE</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -7654,7 +7705,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_07_TAME</t>
+          <t>Req: CA_PROT_06_TAME</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -7671,24 +7722,24 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>CA PROTECTOR — LE GOUGOU</t>
+          <t>CA PROTECTOR — LA CHASSE-GALERIE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>CA Protector — Le Gougou</t>
+          <t>CA Protector — La Chasse-Galerie</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>CA_PROT_08_SUMMON</t>
+          <t>CA_PROT_07_SUMMON</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>THE GOUGOU RISES IN THE CHALEUR BAY — CHAMPLAIN'S MONSTER IS REAL</t>
+          <t>THE FLYING CANOE RUNS THE OTTAWA RIVER — THREE SIGHTINGS, TWO MISSING PATROLS</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -7698,12 +7749,12 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Fires near Chaleur Bay tile</t>
+          <t>Fires near Ottawa River corridor</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Summon/tame chain; grants Le Gougou's Terror mil mod</t>
+          <t>Summon/tame chain; grants La Chasse-Galerie mil mod</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -7715,17 +7766,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CA Protector — Le Gougou</t>
+          <t>CA Protector — La Chasse-Galerie</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CA_PROT_08_TAME</t>
+          <t>CA_PROT_07_TAME</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>THE GOUGOU WITHDRAWS FROM THE BAY LANES — RESTITUTION PROTOCOLS ACTIVE</t>
+          <t>THE FLYING CANOE ACKNOWLEDGES THE REPUBLIC — OTTAWA CORRIDOR SECURED</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -7735,12 +7786,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Req: CA_PROT_08_SUMMON</t>
+          <t>Req: CA_PROT_07_SUMMON</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>→ CA_PROT_08_AGREE</t>
+          <t>→ CA_PROT_07_AGREE</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -7752,35 +7803,153 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
+          <t>CA Protector — La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Req: CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>CA PROTECTOR — LE GOUGOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
           <t>CA Protector — Le Gougou</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>THE GOUGOU RISES IN THE CHALEUR BAY — CHAMPLAIN'S MONSTER IS REAL</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Fires near Chaleur Bay tile</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame chain; grants Le Gougou's Terror mil mod</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CA Protector — Le Gougou</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>THE GOUGOU WITHDRAWS FROM THE BAY LANES — RESTITUTION PROTOCOLS ACTIVE</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Req: CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_08_AGREE</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>CA Protector — Le Gougou</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>CA_PROT_08_AGREE</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE CONTINENTAL ALLIANCE</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Req: CA_PROT_08_TAME</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Protector ally secured</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>FIRST PASS</t>
         </is>
@@ -7788,15 +7957,15 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Haudenosaunee Confederacy</t>
+          <t>Algonquin Nation</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Jessica Clear-Water</t>
+          <t>Jessica Commanda</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Equality/Sovereignty</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5985,27 +5985,27 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Jessica Clear-Water</t>
+          <t>Jessica Commanda</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Named Governor</t>
+          <t>Named Governor (PM)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Haudenosaunee Confederacy</t>
+          <t>Algonquin Nation</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Equality/Sovereignty</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Haudenosaunee representative and diplomat. Bridges Indigenous governance traditions with Continental political structures. Key voice for sovereignty events.</t>
+          <t>Algonquin Prime Minister and diplomat. Carries the governance traditions of the Kitigan Zibi and Pikwakanagan into Continental politics. Named after William Commanda. Key voice for Indigenous sovereignty, treaty rights, and the future shape of the Canadian republic.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Mark Penoit</t>
+          <t>Marc Penoit</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Québécois local leader navigating between French heritage, Crown legacy, and Continental alliance. Events around language rights and provincial autonomy.</t>
+          <t>Québécois local leader navigating between French heritage, Crown legacy, and Continental alliance. Events around language rights, provincial autonomy, and what it means to be Canadien in a republic.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Jessica Commanda</t>
+          <t>Jessica Commanda Odjick</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Jessica Commanda</t>
+          <t>Jessica Commanda Odjick</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>9 CA President arc events — Jessica + Mark Penoit</t>
+          <t>9 CA President arc events — Jessica + Marc Penoit</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Mark Penoit / Pierre Renard (pool)</t>
+          <t>Marc Penoit / Pierre Renard (pool)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -81,7 +81,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +116,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -190,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -213,31 +218,34 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -693,10 +701,12 @@
           <t>Laws</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="B4" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
@@ -942,7 +952,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>UNITED STATES OF AMERICA</t>
         </is>
@@ -1001,47 +1011,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Freedom / Order</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Articles of Confederation</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Foreign Diplomacy</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Constitutional Convention</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Municipal Reform Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Constitutional democracy faction. Adams is the conscience of the movement — events about inclusion and what the revolution is willing to become.</t>
         </is>
@@ -1105,47 +1115,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Freedom Papers</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Underground Railroad</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Universal Emancipation</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Civil Rights Act, Americans with Disabilities Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Abolition-focused faction. Warren is the historian watching the revolution happen — she records everything and forgets nothing.</t>
         </is>
@@ -1209,7 +1219,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>CANADA</t>
         </is>
@@ -1268,47 +1278,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Loyalist Settlers</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Benjamin Tallmadge (pool)</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Crown Defectors</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Pragmatic Compact</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>New Republic Converts</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>National Defence Act, Canada Shipping Act, Dominion Elections Act</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Former Crown loyalists who've accepted the new reality. Provide military discipline and naval expertise. Uneasy but reliable.</t>
         </is>
@@ -1372,47 +1382,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Coureurs des Bois</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Louis Tremblant (pool)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Trade Routes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Frontier Network</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Continental Reach</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>— (no laws currently; wilderness economy focus)</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Wilderness trade network. Know every river, every ridge, every tribe. Invaluable scouts. Culturally distinct from both Crown and Republic.</t>
         </is>
@@ -1541,7 +1551,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN LAWS</t>
         </is>
@@ -1585,32 +1595,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Merchant Marine Act</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>−2 Mandate/Workshop · +2 Gold/Workshop · +1 Gold/Farm · +1 Gold/Camp</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Merchant Marine Act (1920)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>American vessels carry American goods. A strong merchant fleet drives exports and fills the treasury.</t>
         </is>
@@ -1659,32 +1669,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Voting Rights Act</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Voting Rights Act (1965)</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>No citizen shall be denied the right to vote on account of race or condition of previous servitude. The ballot is the foundation of a free Republic.</t>
         </is>
@@ -1733,32 +1743,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act (1990)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>No citizen shall be excluded from civic life on account of disability. The Republic provides for all who cannot provide for themselves.</t>
         </is>
@@ -1807,7 +1817,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>CANADIAN LAWS</t>
         </is>
@@ -1851,32 +1861,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Canada Shipping Act</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>−2 Mandate/Workshop · +2 Gold/Workshop · +1 Gold/Farm · +1 Gold/Camp</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Canada Shipping Act (1936)</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Canadian waters carry Canadian commerce. The Dominion regulates its shipping lanes and expands its mercantile reach.</t>
         </is>
@@ -1925,39 +1935,39 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Dominion Elections Act</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Dominion Elections Act (1920)</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>A single, unified Dominion-wide elections code ensures every eligible citizen may cast a ballot for their representatives.</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>One franchise, one standard, coast to coast. Ottawa's elections code unifies the ballot under federal law and elevates the courthouse as the seat of the democratic compact — no Province stands apart.</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1999,32 +2009,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Accessible Canada Act</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Accessible Canada Act (2019)</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Dominion.</t>
         </is>
@@ -2150,7 +2160,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN DOCTRINES</t>
         </is>
@@ -2204,42 +2214,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Federal Arts Endowment</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>National Endowment for Arts</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>1965</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2298,42 +2308,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>National Monument Act</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Antiquities Act</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>1906</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2392,42 +2402,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>1935</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2486,42 +2496,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>First Amendment</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>1st Amendment (Bill of Rights)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2580,42 +2590,42 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>1910</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2674,7 +2684,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>CANADIAN DOCTRINES</t>
         </is>
@@ -2728,42 +2738,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Canada Council for the Arts Act</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Canada Council for the Arts</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2822,42 +2832,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Historic Sites and Monuments Act</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Historic Sites Act</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2916,42 +2926,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3010,42 +3020,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Charter of Rights and Freedoms</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Canadian Charter of R&amp;F</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3104,42 +3114,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>National Building Code of Canada</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Nat'l Building Code of Canada</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>1941</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3269,7 +3279,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN ICONS</t>
         </is>
@@ -3318,32 +3328,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Benjamin Franklin</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>1706–1790</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Library: +1 Science · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3402,32 +3412,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Alexander Hamilton</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>1755–1804</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3486,32 +3496,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>1743–1826</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Library: +1 Science</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3570,32 +3580,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Harriet Tubman</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>1822–1913</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Combahee River Raid</t>
         </is>
@@ -3654,32 +3664,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Sitting Bull</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>1831–1890</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Little Bighorn Ambush</t>
         </is>
@@ -3738,32 +3748,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Chief Joseph</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>1840–1904</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3822,32 +3832,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Susan B. Anthony</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>1820–1906</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3906,32 +3916,32 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Eleanor Roosevelt</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>1884–1962</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3990,32 +4000,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Cesar Chavez</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>1927–1993</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Barracks: +50 Manpower</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4074,32 +4084,32 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Dolores Huerta</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>1930–</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4116,39 +4126,39 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICONS</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>John A. Macdonald</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>1815–1891</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4207,32 +4217,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Wilfrid Laurier</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>1841–1919</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4291,32 +4301,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Laura Secord</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>1775–1868</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Beaverdams Dispatch</t>
         </is>
@@ -4375,32 +4385,32 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Tommy Douglas</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>1904–1986</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4459,32 +4469,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Lester B. Pearson</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>1897–1972</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Culture, +1 Mandate</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4543,32 +4553,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Emily Murphy</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>1868–1933</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4627,32 +4637,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Terry Fox</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>1958–1981</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4711,32 +4721,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Buffy Sainte-Marie</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>1941–</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4795,32 +4805,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Roméo Dallaire</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>1946–</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Peacekeeping Mandate</t>
         </is>
@@ -4879,32 +4889,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Mary Two-Axe Earley</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>1911–1996</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5022,7 +5032,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN ICON MODS</t>
         </is>
@@ -5221,7 +5231,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICON MODS</t>
         </is>
@@ -5324,7 +5334,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>DOCTRINE MODS</t>
         </is>
@@ -5395,7 +5405,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>AXIS MODS — REASON ↔ PROVIDENCE</t>
         </is>
@@ -5539,7 +5549,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>USA NAMED GOVERNORS &amp; NPCs</t>
         </is>
@@ -5588,37 +5598,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>GOV_02</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Freedom/Diplomat</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>The voice that keeps the movement honest about who it's actually for. Events about inclusion, compromise, and what the revolution is willing to become.</t>
         </is>
@@ -5672,37 +5682,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>GOV_04</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Equality/Patriot</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>The historian watching the revolution happen. What's being recorded matters as much as what's being done. Abolitionist themes throughout.</t>
         </is>
@@ -5756,37 +5766,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>GOV_06</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Ualani Carlisle</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>President (Player)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Federal/Moderate</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>The President. Hawaiian heritage; first woman in the role. The whole game runs through her — she IS the Republic's voice.</t>
         </is>
@@ -5840,37 +5850,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>GOV_08</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Phillis Wheatley</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Named Governor (pool)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>The first published African American poet. Awarded to player via Underground Railroad faction reward. Literary and moral gravitas.</t>
         </is>
@@ -5924,7 +5934,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>CANADIAN GOVERNORS &amp; NPCs</t>
         </is>
@@ -5973,37 +5983,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>NPC_08</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Jessica Commanda Odjick</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Named Governor (PM)</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Algonquin Nation</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Equality/Sovereignty</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Algonquin Prime Minister and diplomat. Carries the governance traditions of the Kitigan Zibi and Pikwakanagan into Continental politics. Named after William Commanda. Key voice for Indigenous sovereignty, treaty rights, and the future shape of the Canadian republic.</t>
         </is>
@@ -6116,7 +6126,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>VICE PRESIDENT RELATIONSHIP ARC  ·  [COMMANDER_NAME] is the player-chosen VP</t>
         </is>
@@ -6443,7 +6453,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>CANADIAN ALLIANCE ARC</t>
         </is>
@@ -6487,32 +6497,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>UK_DECLARATION_01</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>CROWN DECLARES WAR ON THE CONTINENTAL REPUBLIC</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Fires on UK declaration</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Opens Canadian alliance tree; changes diplomatic options</t>
         </is>
@@ -6561,32 +6571,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>CAN_PENOIT_01</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>MARK PENOIT OF THE HABITANTS RECEIVES THE MESSAGE</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Req: can_contact flag</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>→ CAN_CLEARWATER_01; introduces Penoit as CA liaison</t>
         </is>
@@ -6635,32 +6645,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>JOINT OPERATIONS: CONTINENTAL AND CANADIAN FORCES COORDINATE</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Req: CAN_CLEARWATER_01</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>→ CAN_SUMMIT_01; first military cooperation event</t>
         </is>
@@ -6709,32 +6719,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>CAN_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>CONTINENTAL-CANADIAN ALLIANCE FORMALIZED</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Req: CAN_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Sets can_allied flag; major diplomatic milestone</t>
         </is>
@@ -6783,32 +6793,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>THE CANADIAN ELECTION: A CONTINENTAL ALLY WINS</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Req: can_allied</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Bonus loyalty or resource gift; diplomatic goodwill event</t>
         </is>
@@ -6857,32 +6867,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>USA_CALL_01</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>A DISPATCH FROM WASHINGTON — THE AMERICANS WANT TO TALK</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Root (turn 8+, req: uk_buildup_known)</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Sets usa_contact flag; gates USA_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BTN1: Hear them out (→ USA_SUMMIT_01) · BTN2: Decline (sets usa_rejected → CA_ALONE_01)</t>
         </is>
@@ -6931,32 +6941,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>USA_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>THE DOMINION-REPUBLIC ACCORD IS SIGNED</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Branch (req: usa_summit_complete)</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Sets ca_allied flag; mirrors CAN_ALLIANCE_SIGNED from USA side</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Narrative resolution; alliance milestone event</t>
         </is>
@@ -7005,14 +7015,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>CANADIAN PROTECTORS  (8 protectors × 3 events each)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE WENDIGO</t>
         </is>
@@ -7130,7 +7140,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE LOUP-GAROU</t>
         </is>
@@ -7248,7 +7258,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LES FEUX FOLLETS</t>
         </is>
@@ -7366,7 +7376,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — MISHEPESHU</t>
         </is>
@@ -7484,7 +7494,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CORRIVEAU</t>
         </is>
@@ -7602,7 +7612,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE CARCAJOU</t>
         </is>
@@ -7720,7 +7730,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CHASSE-GALERIE</t>
         </is>
@@ -7838,7 +7848,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE GOUGOU</t>
         </is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -702,11 +702,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Responsible government begins at the local level. Each municipality elects its own council to govern in the people's interest.</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>Responsible government runs all the way down. From Baldwin's day onward, every township elects its own council — the courthouse serves the community, not the administrator, and the people who work the land have a say in how it's governed.</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -702,11 +702,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Canadian waters carry Canadian commerce. The Dominion regulates its shipping lanes and expands its mercantile reach.</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>The St. Lawrence is the Dominion's spine. Ottawa consolidates maritime law under one code — Canadian vessels, Canadian rules, Canadian profit. The workshops that outfit the fleet keep more of what they earn.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -702,11 +702,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The right of the people to keep and bear arms shall not be infringed. Citizen militias stand ready to defend the Republic against all tyranny.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>The right of the people to keep and bear arms shall not be infringed. Every farm a muster point, every mansion an armoury — a Republic that arms its citizens does not ask permission to defend itself.</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>American vessels carry American goods. A strong merchant fleet drives exports and fills the treasury.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>American vessels carry American goods. The workshops that outfit the fleet answer to one flag, keep more of what they earn, and the river towns and frontier camps collect a share of every voyage.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Free and fair elections in every township. No appointed official may replace the voice of the people.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>No appointed official may replace the voice of the people. Free elections in every township mean the courthouse runs on consent, not mandate — and the farms and camps that send their people there are better for it.</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>No citizen shall be denied the right to vote on account of race or condition of previous servitude. The ballot is the foundation of a free Republic.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>No citizen shall be denied the ballot on account of race or condition of previous servitude. The franchise is the foundation of the Republic — and the courthouse is where that foundation is enforced.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Discrimination based on race, color, or creed is abolished. All citizens stand equal before the law of this Republic.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>Discrimination based on race, color, or creed is abolished. Every person the Republic governs is a person the Republic answers to — the mandate drops because the people it covers are finally counted.</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>No citizen shall be excluded from civic life on account of disability. The Republic provides for all who cannot provide for themselves.</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>No citizen is excluded from civic life on account of disability. The workshops that adapt their operations keep more of what they produce, and the cost of bringing more people into the Republic's economy falls.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>A unified national defense apparatus ensures no enemy, foreign or domestic, can catch the Republic unprepared.</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>One command, no gaps. The Republic draws its defence under the executive — the barracks run leaner, and every settlement from the frontier to the capital becomes a source of trained manpower.</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Every able-bodied man in the Dominion is liable for militia service. Our communities stand ready to defend the Crown's peace — and now the Republic's.</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>From Confederation onward, the Dominion's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -120,11 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
@@ -141,6 +136,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -218,20 +218,20 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -701,16 +701,12 @@
           <t>Laws</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>11</v>
-      </c>
+      <c r="B4" s="7" t="inlineStr"/>
       <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -952,7 +948,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>UNITED STATES OF AMERICA</t>
         </is>
@@ -1011,47 +1007,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Freedom / Order</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Articles of Confederation</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Foreign Diplomacy</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Constitutional Convention</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Municipal Reform Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Constitutional democracy faction. Adams is the conscience of the movement — events about inclusion and what the revolution is willing to become.</t>
         </is>
@@ -1115,47 +1111,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Freedom Papers</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Underground Railroad</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Universal Emancipation</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Civil Rights Act, Americans with Disabilities Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Abolition-focused faction. Warren is the historian watching the revolution happen — she records everything and forgets nothing.</t>
         </is>
@@ -1219,7 +1215,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>CANADA</t>
         </is>
@@ -1278,47 +1274,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Loyalist Settlers</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Benjamin Tallmadge (pool)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Crown Defectors</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Pragmatic Compact</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>New Republic Converts</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>National Defence Act, Canada Shipping Act, Dominion Elections Act</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Former Crown loyalists who've accepted the new reality. Provide military discipline and naval expertise. Uneasy but reliable.</t>
         </is>
@@ -1382,47 +1378,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Coureurs des Bois</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Louis Tremblant (pool)</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Trade Routes</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Frontier Network</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Continental Reach</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>— (no laws currently; wilderness economy focus)</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Wilderness trade network. Know every river, every ridge, every tribe. Invaluable scouts. Culturally distinct from both Crown and Republic.</t>
         </is>
@@ -1501,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1510,7 +1506,8 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1546,12 +1543,17 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>ICON PATH</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AMERICAN LAWS</t>
         </is>
@@ -1588,44 +1590,46 @@
           <t>The right of the people to keep and bear arms shall not be infringed. Every farm a muster point, every mansion an armoury — a Republic that arms its citizens does not ask permission to defend itself.</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Merchant Marine Act</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>−2 Mandate/Workshop · +2 Gold/Workshop · +1 Gold/Farm · +1 Gold/Camp</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Merchant Marine Act (1920)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>American vessels carry American goods. The workshops that outfit the fleet answer to one flag, keep more of what they earn, and the river towns and frontier camps collect a share of every voyage.</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr"/>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1662,44 +1666,46 @@
           <t>No appointed official may replace the voice of the people. Free elections in every township mean the courthouse runs on consent, not mandate — and the farms and camps that send their people there are better for it.</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Voting Rights Act</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Voting Rights Act (1965)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>No citizen shall be denied the ballot on account of race or condition of previous servitude. The franchise is the foundation of the Republic — and the courthouse is where that foundation is enforced.</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1736,44 +1742,46 @@
           <t>Discrimination based on race, color, or creed is abolished. Every person the Republic governs is a person the Republic answers to — the mandate drops because the people it covers are finally counted.</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act (1990)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>No citizen is excluded from civic life on account of disability. The workshops that adapt their operations keep more of what they produce, and the cost of bringing more people into the Republic's economy falls.</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1810,14 +1818,15 @@
           <t>One command, no gaps. The Republic draws its defence under the executive — the barracks run leaner, and every settlement from the frontier to the capital becomes a source of trained manpower.</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>CANADIAN LAWS</t>
         </is>
@@ -1854,44 +1863,50 @@
           <t>From Confederation onward, the Dominion's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Canada Shipping Act</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>−2 Mandate/Workshop · +2 Gold/Workshop · +1 Gold/Farm · +1 Gold/Camp</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>−1 Mandate/Dock · +2 Gold/Dock · +1 Happiness/Dock</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Canada Shipping Act (1936)</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>The St. Lawrence is the Dominion's spine. Ottawa consolidates maritime law under one code — Canadian vessels, Canadian rules, Canadian profit. The workshops that outfit the fleet keep more of what they earn.</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Every vessel on Canadian waters submits to Dominion safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/can_shipping_act.png</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1928,44 +1943,46 @@
           <t>Responsible government runs all the way down. From Baldwin's day onward, every township elects its own council — the courthouse serves the community, not the administrator, and the people who work the land have a say in how it's governed.</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Dominion Elections Act</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Dominion Elections Act (1920)</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>One franchise, one standard, coast to coast. Ottawa's elections code unifies the ballot under federal law and elevates the courthouse as the seat of the democratic compact — no Province stands apart.</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -2002,44 +2019,46 @@
           <t>All who reside within the Dominion share equal standing before the law, regardless of origin, language, or background.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Accessible Canada Act</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Accessible Canada Act (2019)</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Dominion.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>
         </is>
@@ -2076,7 +2095,8 @@
           <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Dominion's sovereignty is non-negotiable.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>
         </is>
@@ -2084,8 +2104,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2160,7 +2180,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AMERICAN DOCTRINES</t>
         </is>
@@ -2214,42 +2234,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Federal Arts Endowment</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>National Endowment for Arts</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>1965</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2308,42 +2328,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>National Monument Act</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Antiquities Act</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>1906</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2402,42 +2422,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>1935</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2496,42 +2516,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>First Amendment</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>1st Amendment (Bill of Rights)</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2590,42 +2610,42 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>1910</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2684,7 +2704,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>CANADIAN DOCTRINES</t>
         </is>
@@ -2738,42 +2758,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Canada Council for the Arts Act</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Canada Council for the Arts</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2832,42 +2852,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Historic Sites and Monuments Act</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Historic Sites Act</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2926,42 +2946,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3020,42 +3040,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Charter of Rights and Freedoms</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Canadian Charter of R&amp;F</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3114,42 +3134,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>National Building Code of Canada</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Nat'l Building Code of Canada</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>1941</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3279,7 +3299,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AMERICAN ICONS</t>
         </is>
@@ -3328,32 +3348,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Benjamin Franklin</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>1706–1790</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Library: +1 Science · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3412,32 +3432,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Alexander Hamilton</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>1755–1804</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3496,32 +3516,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>1743–1826</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Library: +1 Science</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3580,32 +3600,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Harriet Tubman</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>1822–1913</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Combahee River Raid</t>
         </is>
@@ -3664,32 +3684,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Sitting Bull</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>1831–1890</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Little Bighorn Ambush</t>
         </is>
@@ -3748,32 +3768,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Chief Joseph</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>1840–1904</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3832,32 +3852,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Susan B. Anthony</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>1820–1906</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3916,32 +3936,32 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Eleanor Roosevelt</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>1884–1962</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4000,32 +4020,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Cesar Chavez</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>1927–1993</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Barracks: +50 Manpower</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4084,32 +4104,32 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Dolores Huerta</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>1930–</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4126,39 +4146,39 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>CANADIAN ICONS</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>John A. Macdonald</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>1815–1891</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4217,32 +4237,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Wilfrid Laurier</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>1841–1919</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4301,32 +4321,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Laura Secord</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>1775–1868</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Beaverdams Dispatch</t>
         </is>
@@ -4385,32 +4405,32 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Tommy Douglas</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>1904–1986</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4469,32 +4489,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Lester B. Pearson</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>1897–1972</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Monument: +1 Culture, +1 Mandate</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4553,32 +4573,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Emily Murphy</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>1868–1933</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4637,32 +4657,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Terry Fox</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>1958–1981</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4721,32 +4741,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Buffy Sainte-Marie</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>1941–</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4805,32 +4825,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Roméo Dallaire</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>1946–</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Peacekeeping Mandate</t>
         </is>
@@ -4889,32 +4909,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Mary Two-Axe Earley</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>1911–1996</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5032,7 +5052,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AMERICAN ICON MODS</t>
         </is>
@@ -5231,7 +5251,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>CANADIAN ICON MODS</t>
         </is>
@@ -5549,7 +5569,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>USA NAMED GOVERNORS &amp; NPCs</t>
         </is>
@@ -5598,37 +5618,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>GOV_02</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Freedom/Diplomat</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>The voice that keeps the movement honest about who it's actually for. Events about inclusion, compromise, and what the revolution is willing to become.</t>
         </is>
@@ -5682,37 +5702,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>GOV_04</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Equality/Patriot</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>The historian watching the revolution happen. What's being recorded matters as much as what's being done. Abolitionist themes throughout.</t>
         </is>
@@ -5766,37 +5786,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>GOV_06</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Ualani Carlisle</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>President (Player)</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Federal/Moderate</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>The President. Hawaiian heritage; first woman in the role. The whole game runs through her — she IS the Republic's voice.</t>
         </is>
@@ -5850,37 +5870,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>GOV_08</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Phillis Wheatley</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Named Governor (pool)</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>The first published African American poet. Awarded to player via Underground Railroad faction reward. Literary and moral gravitas.</t>
         </is>
@@ -5934,7 +5954,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>CANADIAN GOVERNORS &amp; NPCs</t>
         </is>
@@ -5983,37 +6003,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>NPC_08</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Jessica Commanda Odjick</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Named Governor (PM)</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Algonquin Nation</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Equality/Sovereignty</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Algonquin Prime Minister and diplomat. Carries the governance traditions of the Kitigan Zibi and Pikwakanagan into Continental politics. Named after William Commanda. Key voice for Indigenous sovereignty, treaty rights, and the future shape of the Canadian republic.</t>
         </is>
@@ -6453,7 +6473,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>CANADIAN ALLIANCE ARC</t>
         </is>
@@ -7015,7 +7035,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>CANADIAN PROTECTORS  (8 protectors × 3 events each)</t>
         </is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Municipal Elections Act, Canadian Citizenship Act, Dominion Elections Act</t>
+          <t>Municipal Elections Act, Canadian Citizenship Act, Republic Elections Act</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>National Defence Act, Canada Shipping Act, Dominion Elections Act</t>
+          <t>National Defence Act, Canada Shipping Act, Republic Elections Act</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>From Confederation onward, the Dominion's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
+          <t>From Confederation onward, the Republic's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Every vessel on Canadian waters submits to Dominion safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
+          <t>Every vessel on Canadian waters submits to Republic safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dominion Elections Act</t>
+          <t>Republic Elections Act</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Dominion Elections Act (1920)</t>
+          <t>Republic Elections Act (1920)</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>All who reside within the Dominion share equal standing before the law, regardless of origin, language, or background.</t>
+          <t>All who reside within the Republic share equal standing before the law, regardless of origin, language, or background.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Dominion.</t>
+          <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Republic.</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Dominion's sovereignty is non-negotiable.</t>
+          <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Republic's sovereignty is non-negotiable.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Dominion Lands Act</t>
+          <t>Republic Lands Act</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Dominion Lands Act</t>
+          <t>Republic Lands Act</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>MARK PENOIT OF THE HABITANTS RECEIVES THE MESSAGE</t>
+          <t>MARC PENOIT OF THE HABITANTS RECEIVES THE MESSAGE</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>THE DOMINION-REPUBLIC ACCORD IS SIGNED</t>
+          <t>THE CANADIAN-CONTINENTAL ACCORD IS SIGNED</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CANADA STANDS ALONE — THE DOMINION DECLINES THE AMERICAN OFFER</t>
+          <t>CANADA STANDS ALONE — THE REPUBLIC DECLINES THE AMERICAN OFFER</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -829,12 +829,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -120,6 +120,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
@@ -136,11 +141,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE0D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -218,20 +218,20 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -827,9 +827,11 @@
           <t>PM Arc (CA)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
@@ -948,7 +950,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>UNITED STATES OF AMERICA</t>
         </is>
@@ -1007,47 +1009,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Freedom / Order</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Articles of Confederation</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Foreign Diplomacy</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Constitutional Convention</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Municipal Reform Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Constitutional democracy faction. Adams is the conscience of the movement — events about inclusion and what the revolution is willing to become.</t>
         </is>
@@ -1111,47 +1113,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Freedom Papers</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Underground Railroad</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Universal Emancipation</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Civil Rights Act, Americans with Disabilities Act, Voting Rights Act</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Abolition-focused faction. Warren is the historian watching the revolution happen — she records everything and forgets nothing.</t>
         </is>
@@ -1215,7 +1217,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>CANADA</t>
         </is>
@@ -1274,47 +1276,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Loyalist Settlers</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Benjamin Tallmadge (pool)</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Crown Defectors</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Pragmatic Compact</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>New Republic Converts</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>National Defence Act, Canada Shipping Act, Republic Elections Act</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Former Crown loyalists who've accepted the new reality. Provide military discipline and naval expertise. Uneasy but reliable.</t>
         </is>
@@ -1378,47 +1380,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Coureurs des Bois</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Louis Tremblant (pool)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Trade Routes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Frontier Network</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Continental Reach</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>— (no laws currently; wilderness economy focus)</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Wilderness trade network. Know every river, every ridge, every tribe. Invaluable scouts. Culturally distinct from both Crown and Republic.</t>
         </is>
@@ -1553,7 +1555,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN LAWS</t>
         </is>
@@ -1591,45 +1593,45 @@
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Merchant Marine Act</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>−2 Mandate/Workshop · +2 Gold/Workshop · +1 Gold/Farm · +1 Gold/Camp</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Merchant Marine Act (1920)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>American vessels carry American goods. The workshops that outfit the fleet answer to one flag, keep more of what they earn, and the river towns and frontier camps collect a share of every voyage.</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1667,45 +1669,45 @@
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Voting Rights Act</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Voting Rights Act (1965)</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>No citizen shall be denied the ballot on account of race or condition of previous servitude. The franchise is the foundation of the Republic — and the courthouse is where that foundation is enforced.</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1743,45 +1745,45 @@
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Americans with Disabilities Act (1990)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>No citizen is excluded from civic life on account of disability. The workshops that adapt their operations keep more of what they produce, and the cost of bringing more people into the Republic's economy falls.</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1819,14 +1821,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>CANADIAN LAWS</t>
         </is>
@@ -1864,49 +1866,49 @@
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Canada Shipping Act</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>−1 Mandate/Dock · +2 Gold/Dock · +1 Happiness/Dock</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Canada Shipping Act (1936)</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Every vessel on Canadian waters submits to Republic safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>art assets/finishedAssets/lawIcons/can_shipping_act.png</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -1944,45 +1946,45 @@
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Republic Elections Act</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Republic Elections Act (1920)</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>One franchise, one standard, coast to coast. Ottawa's elections code unifies the ballot under federal law and elevates the courthouse as the seat of the democratic compact — no Province stands apart.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
@@ -2027,37 +2029,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Accessible Canada Act</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Accessible Canada Act (2019)</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Republic.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr"/>
+      <c r="G16" s="12" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>
@@ -2180,7 +2182,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN DOCTRINES</t>
         </is>
@@ -2234,42 +2236,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Federal Arts Endowment</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>National Endowment for Arts</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>1965</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2328,42 +2330,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>National Monument Act</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Antiquities Act</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>1906</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2422,42 +2424,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Social Security Act</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>1935</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2516,42 +2518,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>First Amendment</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>1st Amendment (Bill of Rights)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2610,42 +2612,42 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Height of Buildings Act</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>1910</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2704,7 +2706,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>CANADIAN DOCTRINES</t>
         </is>
@@ -2758,42 +2760,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Canada Council for the Arts Act</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Canada Council for the Arts</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2852,42 +2854,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Historic Sites and Monuments Act</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Historic Sites Act</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -2946,42 +2948,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Canada Health Act</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3040,42 +3042,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Charter of Rights and Freedoms</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Canadian Charter of R&amp;F</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3134,42 +3136,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>National Building Code of Canada</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Nat'l Building Code of Canada</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>1941</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · +1 Mandate</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
@@ -3299,7 +3301,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN ICONS</t>
         </is>
@@ -3348,32 +3350,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Benjamin Franklin</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>1706–1790</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Library: +1 Science · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3432,32 +3434,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Alexander Hamilton</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>1755–1804</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Workshop: +1 Gold</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3516,32 +3518,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>1743–1826</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Library: +1 Science</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3600,32 +3602,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Harriet Tubman</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>1822–1913</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Combahee River Raid</t>
         </is>
@@ -3684,32 +3686,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Sitting Bull</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>1831–1890</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Little Bighorn Ambush</t>
         </is>
@@ -3768,32 +3770,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Chief Joseph</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>1840–1904</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3852,32 +3854,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Susan B. Anthony</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>1820–1906</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3936,32 +3938,32 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Eleanor Roosevelt</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>1884–1962</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4020,32 +4022,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Cesar Chavez</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>1927–1993</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food · Barracks: +50 Manpower</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4104,32 +4106,32 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Tier 2 – 1800s/Modern</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Dolores Huerta</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>1930–</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4146,39 +4148,39 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICONS</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>John A. Macdonald</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>1815–1891</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4237,32 +4239,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Wilfrid Laurier</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>1841–1919</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Market: +1 Gold · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4321,32 +4323,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Tier 1 – Founding</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Laura Secord</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>1775–1868</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Beaverdams Dispatch</t>
         </is>
@@ -4405,32 +4407,32 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Tommy Douglas</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>1904–1986</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4489,32 +4491,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Lester B. Pearson</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>1897–1972</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Culture, +1 Mandate</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4573,32 +4575,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Emily Murphy</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>1868–1933</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4657,32 +4659,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Terry Fox</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>1958–1981</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4741,32 +4743,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Buffy Sainte-Marie</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>1941–</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4825,32 +4827,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Roméo Dallaire</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>1946–</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Peacekeeping Mandate</t>
         </is>
@@ -4909,32 +4911,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Tier 2 – Modern</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Mary Two-Axe Earley</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>1911–1996</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5052,7 +5054,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>AMERICAN ICON MODS</t>
         </is>
@@ -5251,7 +5253,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICON MODS</t>
         </is>
@@ -5569,7 +5571,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>USA NAMED GOVERNORS &amp; NPCs</t>
         </is>
@@ -5618,37 +5620,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>GOV_02</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Abigail Adams</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Continental Congress</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Freedom/Diplomat</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>The voice that keeps the movement honest about who it's actually for. Events about inclusion, compromise, and what the revolution is willing to become.</t>
         </is>
@@ -5702,37 +5704,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>GOV_04</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Mercy Otis Warren</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Named Governor</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Equality/Patriot</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>The historian watching the revolution happen. What's being recorded matters as much as what's being done. Abolitionist themes throughout.</t>
         </is>
@@ -5786,37 +5788,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>GOV_06</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Ualani Carlisle</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>President (Player)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Federal/Moderate</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>The President. Hawaiian heritage; first woman in the role. The whole game runs through her — she IS the Republic's voice.</t>
         </is>
@@ -5870,37 +5872,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>GOV_08</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Phillis Wheatley</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Named Governor (pool)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Abolitionist League</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Equality</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>The first published African American poet. Awarded to player via Underground Railroad faction reward. Literary and moral gravitas.</t>
         </is>
@@ -5954,7 +5956,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>CANADIAN GOVERNORS &amp; NPCs</t>
         </is>
@@ -6003,37 +6005,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>NPC_08</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Jessica Commanda Odjick</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Named Governor (PM)</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Algonquin Nation</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Equality/Sovereignty</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Algonquin Prime Minister and diplomat. Carries the governance traditions of the Kitigan Zibi and Pikwakanagan into Continental politics. Named after William Commanda. Key voice for Indigenous sovereignty, treaty rights, and the future shape of the Canadian republic.</t>
         </is>
@@ -6473,7 +6475,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>CANADIAN ALLIANCE ARC</t>
         </is>
@@ -7035,7 +7037,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>CANADIAN PROTECTORS  (8 protectors × 3 events each)</t>
         </is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -831,12 +831,12 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -831,12 +831,12 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>−1 Mandate/Population · +1 Happiness/Population</t>
+          <t>−1 Mandate/Population · +1 Harmony/Population</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2018,13 +2018,13 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>All who reside within the Republic share equal standing before the law, regardless of origin, language, or background.</t>
+          <t>For the first time, to live in the Republic is to belong to it. The British subject is gone; in its place, the Canadian citizen — French, Indigenous, newcomer alike, equal before every law that follows. The mandate slips because the Republic has grown wider than before. The harmony rises for exactly the same reason.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>−1 Mandate/Population · +1 Harmony/Population</t>
+          <t>−10% Mandate Cost (All Buildings)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2021,7 +2021,11 @@
           <t>For the first time, to live in the Republic is to belong to it. The British subject is gone; in its place, the Canadian citizen — French, Indigenous, newcomer alike, equal before every law that follows. The mandate slips because the Republic has grown wider than before. The harmony rises for exactly the same reason.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/can_citizenship_act.png</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -720,10 +720,12 @@
           <t>Doctrines</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>11</v>
@@ -2346,7 +2348,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>National Monument Act</t>
+          <t>Landmark Heritage</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -2374,9 +2376,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4016,14 +4016,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Civil rights leader. Monument double-bonus plus courthouse mandate.</t>
+          <t>Baptist minister, Nobel laureate, apostle of nonviolent resistance. Monument yields culture AND mandate — his legacy reshaped civic identity; courthouse yields mandate because his movement forced the law to catch up.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1830,47 +1830,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Homestead Act</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Farm: +1 Food · Camp: +1 Wood</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Homestead Act (1862)</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>One hundred and sixty acres to any citizen willing to work it. The Republic built westward not by conquest alone but by offer — free land, free labour, and the promise that what you cultivate is yours. Every farm a frontier held; every camp a settlement begun.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>CANADIAN LAWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Militia Act</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Freedom</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>+5 Weapons/Mansion lvl · +25 MP/Farm · −1 Mandate/Farm · +1 Mandate/Forge</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Militia Act (1868)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>From Confederation onward, the Republic's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -1882,34 +1882,30 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Canada Shipping Act</t>
+          <t>Militia Act</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>−1 Mandate/Dock · +2 Gold/Dock · +1 Happiness/Dock</t>
+          <t>+5 Weapons/Mansion lvl · +25 MP/Farm · −1 Mandate/Farm · +1 Mandate/Forge</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Canada Shipping Act (1936)</t>
+          <t>Militia Act (1868)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Every vessel on Canadian waters submits to Republic safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/can_shipping_act.png</t>
-        </is>
-      </c>
+          <t>From Confederation onward, the Republic's defence rests on its people. Every farm a recruiting ground, every estate an armoury — the Militia Act turns the countryside into a reserve force that moves the moment the call goes out.</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -1924,30 +1920,34 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Municipal Elections Act</t>
+          <t>Canada Shipping Act</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>−3 Mandate/Courthouse · +1 Happiness/Farm · +1 Happiness/Camp</t>
+          <t>−1 Mandate/Dock · +2 Gold/Dock · +1 Happiness/Dock</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Municipal elections tradition (1849+)</t>
+          <t>Canada Shipping Act (1936)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Responsible government runs all the way down. From Baldwin's day onward, every township elects its own council — the courthouse serves the community, not the administrator, and the people who work the land have a say in how it's governed.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>Every vessel on Canadian waters submits to Republic safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/can_shipping_act.png</t>
+        </is>
+      </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Republic Elections Act</t>
+          <t>Municipal Elections Act</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
+          <t>−3 Mandate/Courthouse · +1 Happiness/Farm · +1 Happiness/Camp</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Republic Elections Act (1920)</t>
+          <t>Municipal elections tradition (1849+)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>One franchise, one standard, coast to coast. Ottawa's elections code unifies the ballot under federal law and elevates the courthouse as the seat of the democratic compact — no Province stands apart.</t>
+          <t>Responsible government runs all the way down. From Baldwin's day onward, every township elects its own council — the courthouse serves the community, not the administrator, and the people who work the land have a say in how it's governed.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr"/>
@@ -2000,34 +2000,30 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Canadian Citizenship Act</t>
+          <t>Republic Elections Act</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>−10% Mandate Cost (All Buildings)</t>
+          <t>−1 Mandate/Province · +1 Max Level Courthouse</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Canadian Citizenship Act (1947)</t>
+          <t>Republic Elections Act (1920)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>For the first time, to live in the Republic is to belong to it. The British subject is gone; in its place, the Canadian citizen — French, Indigenous, newcomer alike, equal before every law that follows. The mandate slips because the Republic has grown wider than before. The harmony rises for exactly the same reason.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/can_citizenship_act.png</t>
-        </is>
-      </c>
+          <t>One franchise, one standard, coast to coast. Ottawa's elections code unifies the ballot under federal law and elevates the courthouse as the seat of the democratic compact — no Province stands apart.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -2042,7 +2038,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Accessible Canada Act</t>
+          <t>Canadian Citizenship Act</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -2052,23 +2048,27 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
+          <t>−10% Mandate Cost (All Buildings)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Accessible Canada Act (2019)</t>
+          <t>Canadian Citizenship Act (1947)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Republic.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>For the first time, to live in the Republic is to belong to it. The British subject is gone; in its place, the Canadian citizen — French, Indigenous, newcomer alike, equal before every law that follows. The mandate slips because the Republic has grown wider than before. The harmony rises for exactly the same reason.</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/can_citizenship_act.png</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -2080,27 +2080,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>National Defence Act</t>
+          <t>Accessible Canada Act</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>−1 Mandate/Barracks · +5 Manpower/all buildings</t>
+          <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>National Defence Act (1922)</t>
+          <t>Accessible Canada Act (2019)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Republic's sovereignty is non-negotiable.</t>
+          <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Republic.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -2110,10 +2110,48 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>National Defence Act</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>−1 Mandate/Barracks · +5 Manpower/all buildings</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>National Defence Act (1922)</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Republic's sovereignty is non-negotiable.</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2301,22 +2339,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Homestead Act</t>
+          <t>Pioneer Heritage</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Homestead Act</t>
+          <t>Frontier Tradition</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1800s</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Camp: +1 Wood</t>
+          <t>Farm: +1 Food · −0.1 Corruption/Farm level/turn</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · −0.1 Corruption/Farm level/turn</t>
+          <t>Farm: +1 Food · −0.1 Corruption/Farm level/turn · Cost: 100 Culture</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>11</v>
@@ -2367,9 +2367,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Federal Arts Endowment</t>
+          <t>Civic Pride</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>National Endowment for Arts</t>
+          <t>National Endowment for the Arts</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Theater/Faire: +1 Culture · Resort: +1 Happiness</t>
+          <t>Resort: +1 Culture · Monument: +0.5 Mandate/level/turn</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>11</v>
@@ -2320,9 +2320,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -725,10 +725,10 @@
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>22</v>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Lacey Wildlife Act</t>
+          <t>Nature Conservationists</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Lacey Act</t>
+          <t>Lacey Act / Conservation Movement</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood</t>
+          <t>Camp: +1 Culture · −0.1 Corruption/Farm &amp; Camp level/turn</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Canada Wildlife Act</t>
+          <t>Nature Conservationists</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Canada Wildlife Act</t>
+          <t>Canada Wildlife Act / Conservation Movement</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood</t>
+          <t>Camp: +1 Culture · −0.1 Corruption/Farm &amp; Camp level/turn</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2797,9 +2797,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>10</v>
@@ -2273,9 +2273,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -2797,9 +2797,9 @@
           <t>Providence</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>+1 Gold/Workshop · −10% Population Upgrade cost</t>
+          <t>+1 Gold/Workshop · +1 Gold/Courthouse · +1 Culture/Courthouse · −10% Population Upgrade cost</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>A barrier-free Canada ensures that disability is no obstacle to full participation in the life of the Republic.</t>
+          <t>No barrier — physical, digital, or architectural — shall prevent a Canadian from full participation in the life of the Republic. Workshops adapt and earn more; courthouses that serve everyone generate more revenue and more culture. The cost of bringing more citizens into the economy falls because the Republic has finally decided they belong there.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2103,7 +2103,11 @@
           <t>No barrier — physical, digital, or architectural — shall prevent a Canadian from full participation in the life of the Republic. Workshops adapt and earn more; courthouses that serve everyone generate more revenue and more culture. The cost of bringing more citizens into the economy falls because the Republic has finally decided they belong there.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/accessible_canada_act.png</t>
+        </is>
+      </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2108,9 +2108,9 @@
           <t>art assets/finishedAssets/lawIcons/accessible_canada_act.png</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>+1 Gold/Workshop · +1 Gold/Courthouse · +1 Culture/Courthouse · −10% Population Upgrade cost</t>
+          <t>+1 Gold/Courthouse · +1 Culture/Courthouse</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1860,7 +1860,11 @@
           <t>One hundred and sixty acres to any citizen willing to work it. The Republic built westward not by conquest alone but by offer — free land, free labour, and the promise that what you cultivate is yours. Every farm a frontier held; every camp a settlement begun.</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>art assets/finishedAssets/lawIcons/homestead_act.png</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>FIRST DRAFT</t>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1865,9 +1865,9 @@
           <t>art assets/finishedAssets/lawIcons/homestead_act.png</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1860,11 +1860,7 @@
           <t>One hundred and sixty acres to any citizen willing to work it. The Republic built westward not by conquest alone but by offer — free land, free labour, and the promise that what you cultivate is yours. Every farm a frontier held; every camp a settlement begun.</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/homestead_act.png</t>
-        </is>
-      </c>
+      <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -1947,11 +1943,7 @@
           <t>Every vessel on Canadian waters submits to Republic safety standards — commercial freighters, fishing trawlers, and the pleasure yachts of whoever thought the St. Lawrence was a private amenity. The docks keep more of what they earn. In exchange, they fill out the forms.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/can_shipping_act.png</t>
-        </is>
-      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -2065,11 +2057,7 @@
           <t>For the first time, to live in the Republic is to belong to it. The British subject is gone; in its place, the Canadian citizen — French, Indigenous, newcomer alike, equal before every law that follows. The mandate slips because the Republic has grown wider than before. The harmony rises for exactly the same reason.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/can_citizenship_act.png</t>
-        </is>
-      </c>
+      <c r="G16" s="12" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
@@ -2107,11 +2095,7 @@
           <t>No barrier — physical, digital, or architectural — shall prevent a Canadian from full participation in the life of the Republic. Workshops adapt and earn more; courthouses that serve everyone generate more revenue and more culture. The cost of bringing more citizens into the economy falls because the Republic has finally decided they belong there.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>art assets/finishedAssets/lawIcons/accessible_canada_act.png</t>
-        </is>
-      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>The Canadian Armed Forces stand on a permanent constitutional footing. The Republic's sovereignty is non-negotiable.</t>
+          <t>The Republic's defence is no longer a wartime improvisation — it is a permanent constitutional obligation. The National Defence Act unified command under federal authority, placing the armed forces on a standing footing that does not wait for the next crisis. Barracks run leaner; every settlement from the coasts to the interior contributes to the reserve.</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -2134,9 +2134,9 @@
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Wilderness Act</t>
+          <t>Inland Maritime Expertise</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Wilderness Act</t>
+          <t>Inland Maritime Expertise</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood · Barracks: +50 Manpower</t>
+          <t>+1 Movement for units starting a turn on Major River or Major Lake tiles</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Doctrine — Wilderness Act / National Parks Act</t>
+          <t>Doctrine — Inland Maritime Expertise / National Parks Act</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2137,6 +2137,82 @@
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>FULL PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>French Language Rights</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>+1 Culture/all Quebec buildings · +10% Manpower/Quebec Barracks · −2 Mandate/Quebec Courthouse</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>French Language Rights (Emergency Recognition Act)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>The Prime Minister has answered the habitants with law. Every building in Quebec now operates in both official tongues of the Republic — the cultural output of the province rises, and the courthouses that administer federal authority in Quebec find their mandate stretched by the weight of recognition.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>French Cultural Identity Enshrined</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Quebec Resort: +1 Culture · +1 Gold · +100 Manpower · −1 Mandate/level · +50% resort dev speed (all CA)</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>French Cultural Identity Enshrined (Cultural Institutes Act)</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>The Republic funds what the Republic claims to value. Québécois cultural institutes receive direct patronage, turning resorts into cultural anchors — profitable, martial, and proud. Every leisure institution the Republic supports is, quietly, also a statement about who it has decided to be.</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16th President. All units +2 Atk +2 Def permanent (mil mod).</t>
+          <t>The president who refused to let the Union dissolve, at the cost of 750,000 lives and his own. Lincoln held together a government, a war, and an argument with history — and signed the document that changed what the war was for. His patronage fills every barracks with soldiers who have something to prove and every courthouse with the weight of law that must, eventually, be lived up to.</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>January 1863: The Emancipation Proclamation transformed the war's moral stakes. Every soldier now fought for something larger than territory.</t>
+          <t>January 1, 1863: The Emancipation Proclamation did not end slavery — it changed what the war was. Every soldier in the field now carried that argument on his bayonet. The cause had a name. The advance became something it hadn't been before.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Emancipation Advance</t>
+          <t>Emancipation Advance / Red Badge of Courage</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The president who refused to let the Union dissolve, at the cost of 750,000 lives and his own. Lincoln held together a government, a war, and an argument with history — and signed the document that changed what the war was for. His patronage fills every barracks with soldiers who have something to prove and every courthouse with the weight of law that must, eventually, be lived up to.</t>
+          <t>The president who refused to let the Union dissolve, at the cost of 750,000 lives and his own. Lincoln held together a government, a war, and an argument with history — and signed the document that changed what the war was for. His patronage fills every barracks with soldiers who have something to prove, every courthouse with the weight of law, and grants rifle units the hardened resilience of men who held the line knowing exactly what it cost.</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5271,27 +5271,27 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Rough Rider's Charge</t>
+          <t>Red Badge of Courage</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Icon — Theodore Roosevelt</t>
+          <t>Icon — Abraham Lincoln</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>infantryMod (terrainMod: Woods)</t>
+          <t>commanderMod (Musket units only)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>+4 Attack, +4 Defense in Woods or Wetlands terrain</t>
+          <t>Rifle units take −5% manpower loss from all combat</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>July 1898: Roosevelt led the Rough Riders charging up San Juan Hill under heavy fire. 'Bully!' he reportedly shouted. No one argued with him.</t>
+          <t>The Civil War infantryman learned something that cannot be taught in peacetime — that the line must hold even when holding it is the worst thing in the world. Those who survived carried that knowledge in their bones, and it showed in the casualty counts.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -5303,27 +5303,27 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>North Star Address</t>
+          <t>Rough Rider's Charge</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Icon — Frederick Douglass</t>
+          <t>Icon — Theodore Roosevelt</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>commanderMod</t>
+          <t>infantryMod (terrainMod: Woods)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Morale loss reduced; rout threshold lowered to 15%</t>
+          <t>+4 Attack, +4 Defense in Woods or Wetlands terrain</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Douglass's oratory — from escaped slave to the Republic's conscience. His newspaper The North Star (1847) gave voice to those the revolution was still failing.</t>
+          <t>July 1898: Roosevelt led the Rough Riders charging up San Juan Hill under heavy fire. 'Bully!' he reportedly shouted. No one argued with him.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -5335,98 +5335,98 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>North Star Address</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Icon — Frederick Douglass</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Morale loss reduced; rout threshold lowered to 15%</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Douglass's oratory — from escaped slave to the Republic's conscience. His newspaper The North Star (1847) gave voice to those the revolution was still failing.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Little Bighorn Ambush</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Icon — Sitting Bull</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>infantryMod (terrainMod: Woods)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>June 1876: Sitting Bull had a vision of soldiers falling like grasshoppers before the battle. The combined Lakota and Cheyenne forces destroyed Custer's 7th Cavalry.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICON MODS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Beaverdams Dispatch</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Icon — Laura Secord</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>commanderMod</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>+3 Defense in Barracks/Fortress tiles</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison held. The Americans surrendered.</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Batoche's Stand</t>
+          <t>Beaverdams Dispatch</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Icon — Louis Riel</t>
+          <t>Icon — Laura Secord</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>infantryMod (terrainMod: Woods)</t>
+          <t>commanderMod</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+          <t>+3 Defense in Barracks/Fortress tiles</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>May 1885: The Métis held Batoche for four days with hunting rifles, kitchen knives, and nails fired from improvised guns. Against a professional army. They lasted longer than anyone expected.</t>
+          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison held. The Americans surrendered.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -5438,172 +5438,204 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Batoche's Stand</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Icon — Louis Riel</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>infantryMod (terrainMod: Woods)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>May 1885: The Métis held Batoche for four days with hunting rifles, kitchen knives, and nails fired from improvised guns. Against a professional army. They lasted longer than anyone expected.</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Peacekeeping Mandate</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Icon — Roméo Dallaire</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>commanderMod</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Morale loss reduced; rout threshold lowered to 15%</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>1994: Dallaire commanded UNAMIR in Rwanda with 2,500 troops and no mandate to stop a genocide. He stayed anyway. His testimony shaped every peacekeeping doctrine that followed.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>DOCTRINE MODS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Woodsman</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Doctrine — Inland Maritime Expertise / National Parks Act</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>infantryMod (terrainMod: Woods)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>The wilderness is not hostile to those who know it. Frontier rangers, trappers, and scouts treat the forest as cover, not obstacle.</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Woodsman</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Doctrine — Inland Maritime Expertise / National Parks Act</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>infantryMod (terrainMod: Woods)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>The wilderness is not hostile to those who know it. Frontier rangers, trappers, and scouts treat the forest as cover, not obstacle.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Vanguard</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Doctrine — Defense Production Act / War Measures Act</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>commanderMod</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>+4 Attack per Level on first engagement in a fresh tile</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Industrial war footing means the army that strikes first has superior materiel. The first charge carries the advantage of preparation.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>AXIS MODS — REASON ↔ PROVIDENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Entrenched</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Axis — Providence III (churchLevel +3)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>commanderMod (entrenchMod)</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>+5 Defense after 3 stationary turns; lost on movement</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>A nation deeply committed to Providence digs in and holds. Faith becomes fortification. The Republic will not be moved from ground it has consecrated.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>Entrenched</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Axis — Providence III (churchLevel +3)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>commanderMod (entrenchMod)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>+5 Defense after 3 stationary turns; lost on movement</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>A nation deeply committed to Providence digs in and holds. Faith becomes fortification. The Republic will not be moved from ground it has consecrated.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Sharpshooter</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Axis — Reason III (churchLevel −3)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>rangedMod</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Ranged attacks ignore 2 enemy Defense per Level</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>An Enlightened Republic trains marksmen, not martyrs. Precision over prayer. The rifle doesn't need divine blessing — it needs a steady hand and a clear eye.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>FIRST PASS</t>
         </is>
@@ -5611,10 +5643,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -766,9 +766,11 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
         <v>14</v>
@@ -5222,7 +5224,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>+5 Attack per Level in first battle round</t>
+          <t>+3 Attack per Level (temp — first-round bonus pending full pass)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -5230,9 +5232,9 @@
           <t>June 1863: Tubman led Col. James Montgomery's gunboats up the Combahee River, freeing 700+ enslaved people. No hesitation. No casualties on her side.</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5320,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>+4 Attack, +4 Defense in Woods or Wetlands terrain</t>
+          <t>+4 Attack, +4 Defense in Woods or Wetlands terrain (temp)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5326,9 +5328,9 @@
           <t>July 1898: Roosevelt led the Rough Riders charging up San Juan Hill under heavy fire. 'Bully!' he reportedly shouted. No one argued with him.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5352,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Morale loss reduced; rout threshold lowered to 15%</t>
+          <t>+2 Defense per Level (temp — rout system pending full pass)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -5358,9 +5360,9 @@
           <t>Douglass's oratory — from escaped slave to the Republic's conscience. His newspaper The North Star (1847) gave voice to those the revolution was still failing.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5384,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain (temp)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5390,9 +5392,9 @@
           <t>June 1876: Sitting Bull had a vision of soldiers falling like grasshoppers before the battle. The combined Lakota and Cheyenne forces destroyed Custer's 7th Cavalry.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5423,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+3 Defense in Barracks/Fortress tiles</t>
+          <t>+3 Defense in Barracks/Fortress tiles (temp)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5429,9 +5431,9 @@
           <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison held. The Americans surrendered.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5455,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain (temp)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -5461,9 +5463,9 @@
           <t>May 1885: The Métis held Batoche for four days with hunting rifles, kitchen knives, and nails fired from improvised guns. Against a professional army. They lasted longer than anyone expected.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5487,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Morale loss reduced; rout threshold lowered to 15%</t>
+          <t>+2 Defense per Level (temp — rout system pending full pass)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -5493,9 +5495,9 @@
           <t>1994: Dallaire commanded UNAMIR in Rwanda with 2,500 troops and no mandate to stop a genocide. He stayed anyway. His testimony shaped every peacekeeping doctrine that followed.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -3704,9 +3704,9 @@
           <t>Emancipation Advance / Red Badge of Courage</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -766,10 +766,10 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Walked 20 miles to warn garrison at Beaverdams (1813). Barracks defense (mil mod).</t>
+          <t>She overheard the American officers planning the attack, and she walked 20 miles through enemy-occupied territory to deliver the warning. The garrison at Beaverdams was ready when the Americans arrived. Barracks yield extra manpower and weapons in her name; Beaverdams Dispatch gives all units +3 Defense per Level when stationed in fortified tiles.</t>
         </is>
       </c>
     </row>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+3 Defense in Barracks/Fortress tiles (temp)</t>
+          <t>+3 Defense per Level in tiles with Barracks or Fortress</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison held. The Americans surrendered.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison was ready. The Americans surrendered.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower, +1 Weapons</t>
+          <t>All units: +2% Defense · Market: +1 Food per level · LOCKED if allied with USA</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>She overheard the American officers planning the attack, and she walked 20 miles through enemy-occupied territory to deliver the warning. The garrison at Beaverdams was ready when the Americans arrived. Barracks yield extra manpower and weapons in her name; Beaverdams Dispatch gives all units +3 Defense per Level when stationed in fortified tiles.</t>
+          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense; Beaverdams Dispatch gives commanders +3 Defense per Level in fortified tiles.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4474,7 +4474,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense; Beaverdams Dispatch gives commanders +3 Defense per Level in fortified tiles.</t>
+          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4467,9 +4467,9 @@
           <t>Beaverdams Dispatch</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4509,14 +4509,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Responsible government architect. Double courthouse mandate bonus.</t>
+          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, every courthouse in the Republic gained teeth. Under LaFontaine, local courts stopped being instruments of colonial administration and became instruments of self-governance. Courthouses yield +2 Mandate instead of +1, representing a population that now believes its institutions belong to it.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +2 Mandate</t>
+          <t>Ottawa &amp; Montreal Courthouse: +1 Gold · +1 Food · +1 Wood · +1 Weapons · +1 Mandate · +1 Culture · +50 Manpower (flat, not per level)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, every courthouse in the Republic gained teeth. Under LaFontaine, local courts stopped being instruments of colonial administration and became instruments of self-governance. Courthouses yield +2 Mandate instead of +1, representing a population that now believes its institutions belong to it.</t>
+          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, the two great cities of the Republic became something more than administrative nodes. The courthouses of Ottawa and Montreal now function as civic engines: every resource the government touches flows through them a little faster, a little more completely. Flat bonus — not per level — because responsible government is not a function of how tall the building is.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Ottawa &amp; Montreal Courthouse: +1 Gold · +1 Food · +1 Wood · +1 Weapons · +1 Mandate · +1 Culture · +50 Manpower (flat, not per level)</t>
+          <t>Ottawa &amp; Montreal Courthouse: +3 Gold · +3 Food · +3 Wood · +3 Weapons · +3 Mandate · +3 Culture · +150 Manpower (flat, not per level)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4509,9 +4509,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4425,14 +4425,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>First female MP (1921). Democracy and education.</t>
+          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Courthouses yield +1 Mandate because she proved that legitimacy expands when more voices are counted. Libraries yield +1 Culture because she understood that exclusion is a kind of ignorance, and education is the remedy.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks): −10 Manpower flat · Farms/Camps/Mines/Forges: +1 Culture flat · Libraries/Monuments/Courthouses/Markets: +1 Science flat</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Courthouses yield +1 Mandate because she proved that legitimacy expands when more voices are counted. Libraries yield +1 Culture because she understood that exclusion is a kind of ignorance, and education is the remedy.</t>
+          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Her influence doesn't make armies larger — it redirects people toward learning, culture, and civic life. Every building that isn't a barracks or a dock loses ten soldiers to the library, the courthouse, the field school. In exchange, the Republic thinks harder and builds more deliberately.</t>
         </is>
       </c>
     </row>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks): −10 Manpower flat · Farms/Camps/Mines/Forges: +1 Culture flat · Libraries/Monuments/Courthouses/Markets: +1 Science flat</t>
+          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
+          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks/Fortress): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -4425,9 +4425,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower, +1 Weapons</t>
+          <t>Ualani: Spirit of the Commander — friendly units adjacent to Ualani gain +15% Attack</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Continental Army commander. Barracks/Fortress +3 Defense (mil mod).</t>
+          <t>Continental Army commander. Grants Ualani the Spirit of the Commander aura mil mod.</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Crossing of the Delaware</t>
+          <t>Spirit of the Commander</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -5187,17 +5187,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>commanderMod</t>
+          <t>ualaniAura</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>+3 Defense in Barracks/Fortress tiles</t>
+          <t>+15% Attack to all friendly units adjacent to Ualani</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>December 1776: Washington crossed the Delaware at midnight in sleet and darkness, surprising the Hessians at Trenton. The gambit saved the revolution.</t>
+          <t>December 1776: Washington crossed the Delaware at midnight in sleet and darkness, surprising the Hessians at Trenton. The gambit saved the revolution. Where the Commander stands, the line holds.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Ualani: Spirit of the Commander — friendly units adjacent to Ualani gain +15% Attack</t>
+          <t>Ualani: Spirit of the General — friendly units adjacent to Ualani gain +15% Attack</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Continental Army commander. Grants Ualani the Spirit of the Commander aura mil mod.</t>
+          <t>Continental Army commander. Grants Ualani the Spirit of the General aura mil mod.</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Spirit of the Commander</t>
+          <t>Spirit of the General</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -3452,9 +3452,9 @@
           <t>Crossing of the Delaware</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -766,14 +766,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4262,93 +4262,93 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 – 1800s/Modern</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>John Brown</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1800–1859</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Harpers Ferry Spark</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Abolitionist who raided Harpers Ferry in 1859. When an enemy army is destroyed: +250 Manpower, +25 Mandate burst to the player country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Tier 2 – 1800s/Modern</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Mary Edwards Walker</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>1832–1919</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Field Surgeon's Gift</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Only woman to receive the Medal of Honor for Civil War service. All armies heal +15% more manpower per turn from reinforcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Tier 1 – Founding</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>John A. Macdonald</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>1815–1891</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>First PM, Confederation architect. Nation-builder bonuses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 – Founding</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>George-Étienne Cartier</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>1814–1873</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Father of Confederation (Quebec). Bilingual law and culture.</t>
         </is>
       </c>
     </row>
@@ -4365,17 +4365,17 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Wilfrid Laurier</t>
+          <t>John A. Macdonald</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>1841–1919</t>
+          <t>1815–1891</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Market: +1 Gold · Monument: +1 Culture</t>
+          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>First French-Canadian PM. Liberal economic prosperity and national pride.</t>
+          <t>First PM, Confederation architect. Nation-builder bonuses.</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4407,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Agnes Macphail</t>
+          <t>George-Étienne Cartier</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>1890–1954</t>
+          <t>1814–1873</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks/Fortress): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
+          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4425,14 +4425,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Her influence doesn't make armies larger — it redirects people toward learning, culture, and civic life. Every building that isn't a barracks or a dock loses ten soldiers to the library, the courthouse, the field school. In exchange, the Republic thinks harder and builds more deliberately.</t>
+          <t>Father of Confederation (Quebec). Bilingual law and culture.</t>
         </is>
       </c>
     </row>
@@ -4449,32 +4449,32 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Laura Secord</t>
+          <t>Wilfrid Laurier</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>1775–1868</t>
+          <t>1841–1919</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>All units: +2% Defense · Market: +1 Food per level · LOCKED if allied with USA</t>
+          <t>Market: +1 Gold · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Beaverdams Dispatch</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense.</t>
+          <t>First French-Canadian PM. Liberal economic prosperity and national pride.</t>
         </is>
       </c>
     </row>
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Louis-Hippolyte LaFontaine</t>
+          <t>Agnes Macphail</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1807–1864</t>
+          <t>1890–1954</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Ottawa &amp; Montreal Courthouse: +3 Gold · +3 Food · +3 Wood · +3 Weapons · +3 Mandate · +3 Culture · +150 Manpower (flat, not per level)</t>
+          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks/Fortress): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, the two great cities of the Republic became something more than administrative nodes. The courthouses of Ottawa and Montreal now function as civic engines: every resource the government touches flows through them a little faster, a little more completely. Flat bonus — not per level — because responsible government is not a function of how tall the building is.</t>
+          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Her influence doesn't make armies larger — it redirects people toward learning, culture, and civic life. Every building that isn't a barracks or a dock loses ten soldiers to the library, the courthouse, the field school. In exchange, the Republic thinks harder and builds more deliberately.</t>
         </is>
       </c>
     </row>
@@ -4528,37 +4528,37 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Tier 2 – Modern</t>
+          <t>Tier 1 – Founding</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Tommy Douglas</t>
+          <t>Laura Secord</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>1904–1986</t>
+          <t>1775–1868</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
+          <t>All units: +2% Defense · Market: +1 Food per level · LOCKED if allied with USA</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>Beaverdams Dispatch</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Father of Canadian medicare. CCF leader. Resort and monument culture.</t>
+          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense.</t>
         </is>
       </c>
     </row>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 – Modern</t>
+          <t>Tier 1 – Founding</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Viola Desmond</t>
+          <t>Louis-Hippolyte LaFontaine</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1882–1965</t>
+          <t>1807–1864</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
+          <t>Ottawa &amp; Montreal Courthouse: +3 Gold · +3 Food · +3 Wood · +3 Weapons · +3 Mandate · +3 Culture · +150 Manpower (flat, not per level)</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4593,14 +4593,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nova Scotia civil rights icon. Refused segregated seating (1946). Library and courthouse.</t>
+          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, the two great cities of the Republic became something more than administrative nodes. The courthouses of Ottawa and Montreal now function as civic engines: every resource the government touches flows through them a little faster, a little more completely. Flat bonus — not per level — because responsible government is not a function of how tall the building is.</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Lester B. Pearson</t>
+          <t>Tommy Douglas</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>1897–1972</t>
+          <t>1904–1986</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Monument: +1 Culture, +1 Mandate</t>
+          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nobel Peace Prize, peacekeeping founder, unified flag designer. Monument double.</t>
+          <t>Father of Canadian medicare. CCF leader. Resort and monument culture.</t>
         </is>
       </c>
     </row>
@@ -4659,32 +4659,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Louis Riel</t>
+          <t>Viola Desmond</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1844–1885</t>
+          <t>1882–1965</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood, +1 Food</t>
+          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Batoche's Stand</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Métis leader, Father of Manitoba. Held Batoche with hunting rifles (1885). Woods terrain (mil mod).</t>
+          <t>Nova Scotia civil rights icon. Refused segregated seating (1946). Library and courthouse.</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Emily Murphy</t>
+          <t>Lester B. Pearson</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>1868–1933</t>
+          <t>1897–1972</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+          <t>Monument: +1 Culture, +1 Mandate</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Famous Five, 'Persons' case (1929). Law reform and civic culture.</t>
+          <t>Nobel Peace Prize, peacekeeping founder, unified flag designer. Monument double.</t>
         </is>
       </c>
     </row>
@@ -4743,32 +4743,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Nellie McClung</t>
+          <t>Louis Riel</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1873–1951</t>
+          <t>1844–1885</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Monument: +1 Culture</t>
+          <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>Batoche's Stand</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Suffragist, Famous Five, temperance advocate. Prairie spirit, farm and monument.</t>
+          <t>Métis leader, Father of Manitoba. Held Batoche with hunting rifles (1885). Woods terrain (mil mod).</t>
         </is>
       </c>
     </row>
@@ -4785,17 +4785,17 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Terry Fox</t>
+          <t>Emily Murphy</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>1958–1981</t>
+          <t>1868–1933</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
+          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Marathon of Hope (1980). Physical endurance and national inspiration.</t>
+          <t>Famous Five, 'Persons' case (1929). Law reform and civic culture.</t>
         </is>
       </c>
     </row>
@@ -4827,17 +4827,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Chief Dan George</t>
+          <t>Nellie McClung</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1899–1981</t>
+          <t>1873–1951</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood · Library: +1 Culture</t>
+          <t>Farm: +1 Food · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tsleil-Waututh Chief, actor, Indigenous rights advocate. Camp and library wisdom.</t>
+          <t>Suffragist, Famous Five, temperance advocate. Prairie spirit, farm and monument.</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Buffy Sainte-Marie</t>
+          <t>Terry Fox</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1941–</t>
+          <t>1958–1981</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Monument: +1 Culture</t>
+          <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Cree artist, activist, educator. Dual culture bonus for arts and heritage.</t>
+          <t>Marathon of Hope (1980). Physical endurance and national inspiration.</t>
         </is>
       </c>
     </row>
@@ -4911,17 +4911,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>David Suzuki</t>
+          <t>Chief Dan George</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1936–</t>
+          <t>1899–1981</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood · Farm: +1 Food</t>
+          <t>Camp: +1 Wood · Library: +1 Culture</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Environmentalist, The Nature of Things. Camp conservation and farm ecology.</t>
+          <t>Tsleil-Waututh Chief, actor, Indigenous rights advocate. Camp and library wisdom.</t>
         </is>
       </c>
     </row>
@@ -4953,32 +4953,32 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Roméo Dallaire</t>
+          <t>Buffy Sainte-Marie</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1946–</t>
+          <t>1941–</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower, +1 Weapons</t>
+          <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Peacekeeping Mandate</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lt. Gen., Rwanda genocide witness, peacekeeping advocate. Morale/rout reduction (mil mod).</t>
+          <t>Cree artist, activist, educator. Dual culture bonus for arts and heritage.</t>
         </is>
       </c>
     </row>
@@ -4995,17 +4995,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Thérèse Casgrain</t>
+          <t>David Suzuki</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>1896–1981</t>
+          <t>1936–</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+          <t>Camp: +1 Wood · Farm: +1 Food</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Quebec suffragist, CCF leader. Law reform and civic culture.</t>
+          <t>Environmentalist, The Nature of Things. Camp conservation and farm ecology.</t>
         </is>
       </c>
     </row>
@@ -5037,32 +5037,32 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley</t>
+          <t>Roméo Dallaire</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>1911–1996</t>
+          <t>1946–</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
+          <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>Peacekeeping Mandate</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mohawk activist. Fought to restore Indigenous women's status under Indian Act.</t>
+          <t>Lt. Gen., Rwanda genocide witness, peacekeeping advocate. Morale/rout reduction (mil mod).</t>
         </is>
       </c>
     </row>
@@ -5079,30 +5079,114 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
+          <t>Thérèse Casgrain</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>1896–1981</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Quebec suffragist, CCF leader. Law reform and civic culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Tier 2 – Modern</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>1911–1996</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mohawk activist. Fought to restore Indigenous women's status under Indian Act.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 – Modern</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
           <t>Pierre Elliott Trudeau</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>1919–2000</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>15th PM, Charter of Rights architect, 'Just Society.' Monument and courthouse.</t>
         </is>
@@ -5110,7 +5194,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -856,14 +856,14 @@
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="4" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8217,16 +8217,1042 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — MOTHMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Mothman</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>THE MOTHMAN OF POINT PLEASANT</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Fires when WV tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Federal Atmospheric Surveillance Act spell</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Mothman</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>PROT_01_TAME</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>MOTHMAN REDIRECTS — CROWN EYES NOW WATCHED</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_01_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_01_AGREE; Mothman observes Crown movements</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Mothman</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>PROT_01_AGREE</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>MOTHMAN FORMALLY ACKNOWLEDGED BY THE DMA</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_01_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; spell added to Presidential Registry</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — JERSEY DEVIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Jersey Devil</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>PROT_02_SUMMON</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>THE PINE BARRENS ARE OFF-LIMITS</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Fires when NJ tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Pine Barrens Development Moratorium spell</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Jersey Devil</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>PROT_02_TAME</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>JERSEY DEVIL REDIRECTS TERRITORIAL AGGRESSION</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_02_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_02_AGREE</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Jersey Devil</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>THE PINE BARRENS ACCORD</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_02_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; spell added to Presidential Registry</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — HEADLESS HORSEMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Headless Horseman</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>THE HORSEMAN RIDES AGAIN</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Fires when NY (Hudson Valley) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Classified Tactical Terror Budget spell</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Headless Horseman</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>HORSEMAN REDIRECTS — CROWN COURIERS TARGETED</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_05_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_05_AGREE</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Headless Horseman</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>PROT_05_AGREE</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>THE HORSEMAN COMMITS TO THE CONTINENTAL CAUSE</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_05_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; spell added to Presidential Registry</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — GOATMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Goatman</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>NO BILLY GOAT I'VE SEEN</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Root (DMA-gated)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Fires when MD tiles 40/41/42 surveyed; consumes dmaInvestigationPending flag</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Objective 1: MD library+barracks targets met → TAME; grants Goatman's Judgement mil mod/spell</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Goatman</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>GOATMAN: CONSEQUENCES</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_06_summoned flag; MD lib+barracks objective met</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_06_AGREE; Objective 2: MD total buildings ≥ 100</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Goatman</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>PROT_06_AGREE</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>MIDNIGHT MEETING — THE TERMS OF THE DEAL</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_06_tame flag; MD buildings ≥ 100</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>BTN1: agreement · BTN2 (explicit) → PROT_06_AGREE_INTIMATE; uses [CMD_POSSESSIVE] token</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Goatman</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>PROT_06_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>VOYEUR, NOT MONSTER</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intimate</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Req: BTN2 on PROT_06_AGREE</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Sets prot_06_agreed flag; Warm/Tender tone</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — BELL WITCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Bell Witch</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>THE BELL WITCH MANIFESTS IN TENNESSEE</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Fires when Nashville (tile 165) owned; standard summon check</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Objective hint: TN culture+food ≥ 25 → TAME; grants Bell Witch's Gift spell (milmod: Giant Green Futa Dong +3 Atk/3 turns)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Bell Witch</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>THE HAUNTING OF BELL HOUSE</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_07_summoned flag; TN culture+food ≥ 25</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>→ PROT_07_AGREE; Objective 2: TN culture+food ≥ 40</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Bell Witch</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>PROT_07_AGREE</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>JINGLE BELLS, KING GEORGE SMELLS</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_07_tame flag; TN culture+food ≥ 40</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>BTN1: 'The meeting is enough' → prot_07_agreed · BTN2 (explicit) → PROT_07_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Bell Witch</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>PROT_07_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>BELL AND THE BEAST</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Intimate</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Req: BTN2 on PROT_07_AGREE</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Sets prot_07_agreed flag; the velvet case; Warm/Tender tone</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — OLD IRONSIDES</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Old Ironsides</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>OLD IRONSIDES SPOTTED ROVING THE COASTAL WATERS</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Root (DMA-gated)</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Fires when MA coastal tile investigated; consumes dmaInvestigationPending flag</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Naval Superiority Maintenance Directive spell</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Old Ironsides</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>PRESIDENT UALANI MEETS WITH OLD IRONSIDES</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_08_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_08_AGREE; two-hour meeting on USS Constitution</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Old Ironsides</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>PROT_08_AGREE</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>PRESIDENT UALANI SETS SAIL</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_08_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; Constitution joins Continental Navy</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — AGENT 355</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Agent 355</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>PROT_16_SUMMON</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>CULPER RING CONTACT ESTABLISHED — MANHATTAN ASSET ACTIVE</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Root (DMA-gated)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Fires when Manhattan tiles 20/190/191 investigated; consumes dmaInvestigationPending</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Objective: playerSpyWins ≥ 3 → TAME; grants Culper Ring spell (enemy tile -5% shield/turn + reveal)</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Agent 355</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>PROT_16_TAME</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>CULPER RING OPERATIONAL — CONTINENTAL INTELLIGENCE EXPANDS</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_16_summoned flag; playerSpyWins ≥ 3</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_16_AGREE; Objective 2: playerSpyWins ≥ 6</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Agent 355</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>PROT_16_AGREE</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>AGENT 355 FORMALLY ACKNOWLEDGED — THE CULPER NETWORK IS YOURS</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_16_tame flag; playerSpyWins ≥ 6</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_16_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — LINCOLN'S GHOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>PROT_17_SUMMON</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>LINCOLN'S GHOST HAS BEEN SEEN IN THE WHITE HOUSE EAST WING</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Root (DMA-gated)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Fires when DC tile investigated; consumes dmaInvestigationPending</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Emancipation Proclamation 2 spell</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>PROT_17_TAME</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>LINCOLN'S GHOST ACKNOWLEDGES THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_17_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_17_AGREE</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>PROT_17_AGREE</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>LINCOLN'S GHOST FORMALLY COMMITS TO THE CONTINENTAL CAUSE</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_17_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_17_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="18">
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A77:G77"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -856,14 +856,14 @@
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="4" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9235,25 +9235,739 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — WOOD BOOGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Wood Booger</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>PROT_03_SUMMON</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>BIGFOOT SIDES WITH THE REVOLUTION</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Fires when NC (Blue Ridge/Asheville) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Appalachian Privacy Protection Act spell</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Wood Booger</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>PROT_03_TAME</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>APPALACHIAN PASSES REOPEN: BIGFOOT ACKNOWLEDGES THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_03_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_03_AGREE; mountain passes opened</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Wood Booger</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>PROT_03_AGREE</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUGH THE MOUNTAINS</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_03_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — PAMOLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Pamola</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>PROT_04_SUMMON</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>PAMOLA STIRS ABOVE KATAHDIN</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Fires when ME (Bar Harbor/Acadia) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Executive Weather Control Initiative spell; school: storm</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Pamola</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>PROT_04_TAME</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>PAMOLA WITHDRAWS — STORM ACTIVITY OVER ACADIA NORMALIZES</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_04_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_04_AGREE; Penobscot Nation liaison ceremony</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Pamola</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>PROT_04_AGREE</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>PAMOLA FORMALLY ALIGNS WITH THE CONTINENTAL REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_04_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_04_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — SNALLYGASTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Snallygaster</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>PROT_10_SUMMON</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>THE SNALLYGASTER DESCENDS ON VIRGINIA</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Fires when VA (Winchester/Shenandoah Valley) tile contested; DMA investigation required</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Inter-Agency Cryptid Integration Program spell</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Snallygaster</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>PROT_10_TAME</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>SNALLYGASTER REDIRECTS — CONTINENTAL SUPPLY ROUTES NOW CLEAR</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_10_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_10_AGREE; feeding station established in Shenandoah</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Snallygaster</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>PROT_10_AGREE</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY NETWORK</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_10_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_10_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — BLACK DOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Black Dog</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>PROT_11_SUMMON</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>THE BLACK DOG OF THE HANGING HILLS</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Fires when CT (Hartford/Hanging Hills) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Black Dog Watch Protocol spell; school: cryptid</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Black Dog</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>PROT_11_TAME</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>BLACK DOG REDIRECTED — CONTINENTAL PATROL ROUTES CLEARED</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_11_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_11_AGREE; omen redirected toward Crown forces</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Black Dog</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>PROT_11_AGREE</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>BLACK DOG FORMALLY WATCHES THE HANGING HILLS FOR THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_11_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_11_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — MERCY BROWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Mercy Brown</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>PROT_12_SUMMON</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>MERCY BROWN STIRS IN EXETER CHURCHYARD</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Fires when RI (Coventry/Exeter) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Mercy Brown's Compact spell; school: spectral</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Mercy Brown</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>PROT_12_TAME</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>MERCY BROWN WITHDRAWS FROM CONTINENTAL FORCES — RHODE ISLAND GARRISONS RECOVERING</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_12_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_12_AGREE; DMA cemetery visit establishes contact</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Mercy Brown</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>PROT_12_AGREE</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>MERCY BROWN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_12_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_12_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>USA PROTECTOR — CHAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Champ</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>PROT_13_SUMMON</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>CHAMP SURFACES ON LAKE CHAMPLAIN</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Fires when VT (Montpelier/Lake Champlain region) tile contested; standard summon check</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Summon/tame/agreement chain; grants Lake Champlain Sovereignty Decree spell; school: cryptid</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>USA Protector — Champ</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>PROT_13_TAME</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>CHAMP DISTINGUISHES CONTINENTAL VESSELS — LAKE CHAMPLAIN CROSSINGS RESTORED</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Req: prot_13_summoned flag + objective met</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>→ PROT_13_AGREE; vessel white-stripe marking protocol</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>USA Protector — Champ</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>PROT_13_AGREE</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>CHAMP FORMALLY GUARDS LAKE CHAMPLAIN FOR THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Req: prot_13_tame flag + objective met</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Protector ally secured; BTN2 (explicit) → PROT_13_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A89:G89"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A101:G101"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -195,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,13 +239,16 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3359,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3602,17 +3611,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Phillis Wheatley</t>
+          <t>Eliza Schuyler Hamilton</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1753–1784</t>
+          <t>1757–1854</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Monument: +1 Culture</t>
+          <t>Market: +1 Mandate/lvl · Courthouse: −1 Moral Decay/turn</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3620,14 +3629,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>INTEGRATED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>First published African American poet. Dual culture bonus.</t>
+          <t>She outlived Hamilton by 50 years; preserved his legacy and built orphanages. Commerce with conscience; justice that does not rot.</t>
         </is>
       </c>
     </row>
@@ -3644,17 +3653,17 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Phillis Wheatley</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>1743–1826</t>
+          <t>1753–1784</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Library: +1 Science</t>
+          <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -3669,7 +3678,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Author of the Declaration, gentleman farmer, scholar. Farm and library.</t>
+          <t>First published African American poet. Dual culture bonus.</t>
         </is>
       </c>
     </row>
@@ -3681,37 +3690,37 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 – 1800s/Modern</t>
+          <t>Tier 1 – Founding</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1809–1865</t>
+          <t>1743–1826</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower · Courthouse: +1 Mandate</t>
+          <t>Farm: +1 Food · Library: +1 Science</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Emancipation Advance / Red Badge of Courage</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The president who refused to let the Union dissolve, at the cost of 750,000 lives and his own. Lincoln held together a government, a war, and an argument with history — and signed the document that changed what the war was for. His patronage fills every barracks with soldiers who have something to prove, every courthouse with the weight of law, and grants rifle units the hardened resilience of men who held the line knowing exactly what it cost.</t>
+          <t>Author of the Declaration, gentleman farmer, scholar. Farm and library.</t>
         </is>
       </c>
     </row>
@@ -3728,32 +3737,32 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Harriet Tubman</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>1822–1913</t>
+          <t>1809–1865</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower, +1 Weapons</t>
+          <t>Barracks: +50 Manpower · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Combahee River Raid</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>Emancipation Advance / Red Badge of Courage</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Underground Railroad conductor, Union spy. +5 Atk first battle round (mil mod).</t>
+          <t>The president who refused to let the Union dissolve, at the cost of 750,000 lives and his own. Lincoln held together a government, a war, and an argument with history — and signed the document that changed what the war was for. His patronage fills every barracks with soldiers who have something to prove, every courthouse with the weight of law, and grants rifle units the hardened resilience of men who held the line knowing exactly what it cost.</t>
         </is>
       </c>
     </row>
@@ -3770,22 +3779,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Harriet Tubman</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1818–1895</t>
+          <t>1822–1913</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
+          <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>North Star Address</t>
+          <t>Combahee River Raid</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -3795,7 +3804,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Abolitionist orator. Morale loss reduced, rout threshold 15% (mil mod).</t>
+          <t>Underground Railroad conductor, Union spy. +5 Atk first battle round (mil mod).</t>
         </is>
       </c>
     </row>
@@ -3812,22 +3821,22 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Sitting Bull</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1831–1890</t>
+          <t>1818–1895</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood, +1 Food</t>
+          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Little Bighorn Ambush</t>
+          <t>North Star Address</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3837,7 +3846,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hunkpapa Lakota chief. +2 Atk +2 Def in Woods terrain (mil mod).</t>
+          <t>Abolitionist orator. Morale loss reduced, rout threshold 15% (mil mod).</t>
         </is>
       </c>
     </row>
@@ -3854,22 +3863,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sojourner Truth</t>
+          <t>Sitting Bull</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1797–1883</t>
+          <t>1831–1890</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Monument: +1 Culture</t>
+          <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Little Bighorn Ambush</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -3879,7 +3888,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Abolitionist and women's rights activist. Farm and monument culture.</t>
+          <t>Hunkpapa Lakota chief. +2 Atk +2 Def in Woods terrain (mil mod).</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3905,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Chief Joseph</t>
+          <t>Sojourner Truth</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>1840–1904</t>
+          <t>1797–1883</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate</t>
+          <t>Farm: +1 Food · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -3921,7 +3930,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nez Perce leader. 'I will fight no more forever.' Courthouse justice.</t>
+          <t>Abolitionist and women's rights activist. Farm and monument culture.</t>
         </is>
       </c>
     </row>
@@ -3938,22 +3947,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Theodore Roosevelt</t>
+          <t>Chief Joseph</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1858–1919</t>
+          <t>1840–1904</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Mine: +1 Metal · Camp: +1 Wood · Barracks: +50 Manpower</t>
+          <t>Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Rough Rider's Charge</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -3963,7 +3972,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Conservationist, Rough Rider. +4 Atk +4 Def in Woods/Wetlands (mil mod).</t>
+          <t>Nez Perce leader. 'I will fight no more forever.' Courthouse justice.</t>
         </is>
       </c>
     </row>
@@ -3980,22 +3989,22 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Susan B. Anthony</t>
+          <t>Theodore Roosevelt</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>1820–1906</t>
+          <t>1858–1919</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
+          <t>Mine: +1 Metal · Camp: +1 Wood · Barracks: +50 Manpower</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rough Rider's Charge</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -4005,7 +4014,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Suffragist. Vote and civic culture. Courthouse and monument bonus.</t>
+          <t>Conservationist, Rough Rider. +4 Atk +4 Def in Woods/Wetlands (mil mod).</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4031,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Ida B. Wells</t>
+          <t>Susan B. Anthony</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1862–1931</t>
+          <t>1820–1906</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture</t>
+          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4047,7 +4056,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Investigative journalist, anti-lynching crusader. Library culture.</t>
+          <t>Suffragist. Vote and civic culture. Courthouse and monument bonus.</t>
         </is>
       </c>
     </row>
@@ -4064,17 +4073,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Eleanor Roosevelt</t>
+          <t>Ida B. Wells</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>1884–1962</t>
+          <t>1862–1931</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
+          <t>Library: +1 Culture</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -4089,7 +4098,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>UN diplomat, First Lady, human rights architect. Resort and monument.</t>
+          <t>Investigative journalist, anti-lynching crusader. Library culture.</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4115,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Martin Luther King Jr.</t>
+          <t>Eleanor Roosevelt</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1929–1968</t>
+          <t>1884–1962</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Monument: +1 Culture, +1 Mandate · Courthouse: +1 Mandate</t>
+          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4124,14 +4133,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Baptist minister, Nobel laureate, apostle of nonviolent resistance. Monument yields culture AND mandate — his legacy reshaped civic identity; courthouse yields mandate because his movement forced the law to catch up.</t>
+          <t>UN diplomat, First Lady, human rights architect. Resort and monument.</t>
         </is>
       </c>
     </row>
@@ -4148,17 +4157,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Cesar Chavez</t>
+          <t>Martin Luther King Jr.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>1927–1993</t>
+          <t>1929–1968</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Barracks: +50 Manpower</t>
+          <t>Monument: +1 Culture, +1 Mandate · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -4166,14 +4175,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UFW co-founder. Farm labor and manpower bonus.</t>
+          <t>Baptist minister, Nobel laureate, apostle of nonviolent resistance. Monument yields culture AND mandate — his legacy reshaped civic identity; courthouse yields mandate because his movement forced the law to catch up.</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4199,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Jimmy Carter</t>
+          <t>Cesar Chavez</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>1924–2024</t>
+          <t>1927–1993</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Resort: +1 Happiness</t>
+          <t>Farm: +1 Food · Barracks: +50 Manpower</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4215,7 +4224,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>39th President, habitat builder, peacemaker. Farm and resort.</t>
+          <t>UFW co-founder. Farm labor and manpower bonus.</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4241,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Dolores Huerta</t>
+          <t>Jimmy Carter</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>1930–</t>
+          <t>1924–2024</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Farm: +1 Food</t>
+          <t>Farm: +1 Food · Resort: +1 Happiness</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -4257,7 +4266,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>UFW co-founder. ¡Sí, se puede! Farm labor bonus.</t>
+          <t>39th President, habitat builder, peacemaker. Farm and resort.</t>
         </is>
       </c>
     </row>
@@ -4274,24 +4283,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>John Brown</t>
+          <t>Dolores Huerta</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1800–1859</t>
+          <t>1930–</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
+          <t>Farm: +1 Food</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Harpers Ferry Spark</t>
-        </is>
-      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>FIRST PASS</t>
@@ -4299,7 +4308,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Abolitionist who raided Harpers Ferry in 1859. When an enemy army is destroyed: +250 Manpower, +25 Mandate burst to the player country.</t>
+          <t>UFW co-founder. ¡Sí, se puede! Farm labor bonus.</t>
         </is>
       </c>
     </row>
@@ -4316,81 +4325,81 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
+          <t>John Brown</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>1800–1859</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Harpers Ferry Spark</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Abolitionist who raided Harpers Ferry in 1859. When an enemy army is destroyed: +250 Manpower, +25 Mandate burst to the player country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 – 1800s/Modern</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t>Mary Edwards Walker</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>1832–1919</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Field Surgeon's Gift</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Only woman to receive the Medal of Honor for Civil War service. All armies heal +15% more manpower per turn from reinforcement.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>CANADIAN ICONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Tier 1 – Founding</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>John A. Macdonald</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>1815–1891</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>First PM, Confederation architect. Nation-builder bonuses.</t>
         </is>
       </c>
     </row>
@@ -4407,17 +4416,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>George-Étienne Cartier</t>
+          <t>John A. Macdonald</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>1814–1873</t>
+          <t>1815–1891</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
+          <t>Courthouse: +1 Mandate · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4432,7 +4441,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Father of Confederation (Quebec). Bilingual law and culture.</t>
+          <t>First PM, Confederation architect. Nation-builder bonuses.</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4458,17 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Wilfrid Laurier</t>
+          <t>George-Étienne Cartier</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>1841–1919</t>
+          <t>1814–1873</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Market: +1 Gold · Monument: +1 Culture</t>
+          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -4474,7 +4483,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>First French-Canadian PM. Liberal economic prosperity and national pride.</t>
+          <t>Father of Confederation (Quebec). Bilingual law and culture.</t>
         </is>
       </c>
     </row>
@@ -4491,17 +4500,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Agnes Macphail</t>
+          <t>Wilfrid Laurier</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1890–1954</t>
+          <t>1841–1919</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks/Fortress): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
+          <t>Market: +1 Gold · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4509,14 +4518,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Her influence doesn't make armies larger — it redirects people toward learning, culture, and civic life. Every building that isn't a barracks or a dock loses ten soldiers to the library, the courthouse, the field school. In exchange, the Republic thinks harder and builds more deliberately.</t>
+          <t>First French-Canadian PM. Liberal economic prosperity and national pride.</t>
         </is>
       </c>
     </row>
@@ -4533,22 +4542,22 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Laura Secord</t>
+          <t>Agnes Macphail</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>1775–1868</t>
+          <t>1890–1954</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>All units: +2% Defense · Market: +1 Food per level · LOCKED if allied with USA</t>
+          <t>Courthouse: +1 Mandate/level · Library: +1 Culture/level · All buildings (not Dock/Barracks/Fortress): −10 Manpower flat · Farms/Camps/Mines/Forges/Granaries: +1 Culture flat · Libraries/Monuments/Courthouses/Markets/Resorts: +1 Science flat</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Beaverdams Dispatch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -4558,7 +4567,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense.</t>
+          <t>She was told she didn't belong there. She went anyway, and then she went back, and then she went back again — six consecutive terms. The first woman elected to the House of Commons, she spent her career arguing that democracy only works if it actually includes people. Her influence doesn't make armies larger — it redirects people toward learning, culture, and civic life. Every building that isn't a barracks or a dock loses ten soldiers to the library, the courthouse, the field school. In exchange, the Republic thinks harder and builds more deliberately.</t>
         </is>
       </c>
     </row>
@@ -4575,22 +4584,22 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Louis-Hippolyte LaFontaine</t>
+          <t>Laura Secord</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1807–1864</t>
+          <t>1775–1868</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Ottawa &amp; Montreal Courthouse: +3 Gold · +3 Food · +3 Wood · +3 Weapons · +3 Mandate · +3 Culture · +150 Manpower (flat, not per level)</t>
+          <t>All units: +2% Defense · Market: +1 Food per level · LOCKED if allied with USA</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Beaverdams Dispatch</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -4600,7 +4609,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, the two great cities of the Republic became something more than administrative nodes. The courthouses of Ottawa and Montreal now function as civic engines: every resource the government touches flows through them a little faster, a little more completely. Flat bonus — not per level — because responsible government is not a function of how tall the building is.</t>
+          <t>She overheard the American officers planning the attack and walked 20 miles through enemy-occupied territory to deliver the warning. The garrison held. She cannot be selected if Canada has allied with the United States — she warned against them in 1813, and that is not a small thing. Markets yield +1 Food per level in her name; all units gain +2% Defense.</t>
         </is>
       </c>
     </row>
@@ -4612,22 +4621,22 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Tier 2 – Modern</t>
+          <t>Tier 1 – Founding</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Tommy Douglas</t>
+          <t>Louis-Hippolyte LaFontaine</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>1904–1986</t>
+          <t>1807–1864</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
+          <t>Ottawa &amp; Montreal Courthouse: +3 Gold · +3 Food · +3 Wood · +3 Weapons · +3 Mandate · +3 Culture · +150 Manpower (flat, not per level)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -4635,14 +4644,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Father of Canadian medicare. CCF leader. Resort and monument culture.</t>
+          <t>He argued that the elected assembly — not the appointed council — must control the executive. That argument won, and when it did, the two great cities of the Republic became something more than administrative nodes. The courthouses of Ottawa and Montreal now function as civic engines: every resource the government touches flows through them a little faster, a little more completely. Flat bonus — not per level — because responsible government is not a function of how tall the building is.</t>
         </is>
       </c>
     </row>
@@ -4659,17 +4668,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Viola Desmond</t>
+          <t>Tommy Douglas</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1882–1965</t>
+          <t>1904–1986</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
+          <t>Resort: +1 Happiness · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -4684,7 +4693,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nova Scotia civil rights icon. Refused segregated seating (1946). Library and courthouse.</t>
+          <t>Father of Canadian medicare. CCF leader. Resort and monument culture.</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4710,17 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Lester B. Pearson</t>
+          <t>Viola Desmond</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>1897–1972</t>
+          <t>1882–1965</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Monument: +1 Culture, +1 Mandate</t>
+          <t>Library: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -4726,7 +4735,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nobel Peace Prize, peacekeeping founder, unified flag designer. Monument double.</t>
+          <t>Nova Scotia civil rights icon. Refused segregated seating (1946). Library and courthouse.</t>
         </is>
       </c>
     </row>
@@ -4743,32 +4752,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Louis Riel</t>
+          <t>Lester B. Pearson</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1844–1885</t>
+          <t>1897–1972</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood, +1 Food</t>
+          <t>Monument: +1 Culture, +1 Mandate</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Batoche's Stand</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Métis leader, Father of Manitoba. Held Batoche with hunting rifles (1885). Woods terrain (mil mod).</t>
+          <t>Nobel Peace Prize, peacekeeping founder, unified flag designer. Monument double.</t>
         </is>
       </c>
     </row>
@@ -4785,32 +4794,32 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Emily Murphy</t>
+          <t>Louis Riel</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>1868–1933</t>
+          <t>1844–1885</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+          <t>Camp: +1 Wood, +1 Food</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>Batoche's Stand</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Famous Five, 'Persons' case (1929). Law reform and civic culture.</t>
+          <t>Métis leader, Father of Manitoba. Held Batoche with hunting rifles (1885). Woods terrain (mil mod).</t>
         </is>
       </c>
     </row>
@@ -4827,17 +4836,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Nellie McClung</t>
+          <t>Emily Murphy</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1873–1951</t>
+          <t>1868–1933</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Farm: +1 Food · Monument: +1 Culture</t>
+          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -4852,7 +4861,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Suffragist, Famous Five, temperance advocate. Prairie spirit, farm and monument.</t>
+          <t>Famous Five, 'Persons' case (1929). Law reform and civic culture.</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4878,17 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Terry Fox</t>
+          <t>Nellie McClung</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1958–1981</t>
+          <t>1873–1951</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
+          <t>Farm: +1 Food · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -4894,7 +4903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Marathon of Hope (1980). Physical endurance and national inspiration.</t>
+          <t>Suffragist, Famous Five, temperance advocate. Prairie spirit, farm and monument.</t>
         </is>
       </c>
     </row>
@@ -4911,17 +4920,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Chief Dan George</t>
+          <t>Terry Fox</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1899–1981</t>
+          <t>1958–1981</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood · Library: +1 Culture</t>
+          <t>Barracks: +50 Manpower · Resort: +1 Happiness</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -4936,7 +4945,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tsleil-Waututh Chief, actor, Indigenous rights advocate. Camp and library wisdom.</t>
+          <t>Marathon of Hope (1980). Physical endurance and national inspiration.</t>
         </is>
       </c>
     </row>
@@ -4953,17 +4962,17 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Buffy Sainte-Marie</t>
+          <t>Chief Dan George</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1941–</t>
+          <t>1899–1981</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Library: +1 Culture · Monument: +1 Culture</t>
+          <t>Camp: +1 Wood · Library: +1 Culture</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -4978,7 +4987,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cree artist, activist, educator. Dual culture bonus for arts and heritage.</t>
+          <t>Tsleil-Waututh Chief, actor, Indigenous rights advocate. Camp and library wisdom.</t>
         </is>
       </c>
     </row>
@@ -4995,17 +5004,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>David Suzuki</t>
+          <t>Buffy Sainte-Marie</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>1936–</t>
+          <t>1941–</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Camp: +1 Wood · Farm: +1 Food</t>
+          <t>Library: +1 Culture · Monument: +1 Culture</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5020,7 +5029,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Environmentalist, The Nature of Things. Camp conservation and farm ecology.</t>
+          <t>Cree artist, activist, educator. Dual culture bonus for arts and heritage.</t>
         </is>
       </c>
     </row>
@@ -5037,32 +5046,32 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Roméo Dallaire</t>
+          <t>David Suzuki</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>1946–</t>
+          <t>1936–</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Barracks: +50 Manpower, +1 Weapons</t>
+          <t>Camp: +1 Wood · Farm: +1 Food</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Peacekeeping Mandate</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Lt. Gen., Rwanda genocide witness, peacekeeping advocate. Morale/rout reduction (mil mod).</t>
+          <t>Environmentalist, The Nature of Things. Camp conservation and farm ecology.</t>
         </is>
       </c>
     </row>
@@ -5079,32 +5088,32 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Thérèse Casgrain</t>
+          <t>Roméo Dallaire</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>1896–1981</t>
+          <t>1946–</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
+          <t>Barracks: +50 Manpower, +1 Weapons</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>Peacekeeping Mandate</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Quebec suffragist, CCF leader. Law reform and civic culture.</t>
+          <t>Lt. Gen., Rwanda genocide witness, peacekeeping advocate. Morale/rout reduction (mil mod).</t>
         </is>
       </c>
     </row>
@@ -5121,17 +5130,17 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley</t>
+          <t>Thérèse Casgrain</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1911–1996</t>
+          <t>1896–1981</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
+          <t>Courthouse: +1 Mandate · Library: +1 Culture</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -5146,7 +5155,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mohawk activist. Fought to restore Indigenous women's status under Indian Act.</t>
+          <t>Quebec suffragist, CCF leader. Law reform and civic culture.</t>
         </is>
       </c>
     </row>
@@ -5163,30 +5172,72 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
+          <t>Mary Two-Axe Earley</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>1911–1996</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Courthouse: +1 Mandate · Farm: +1 Food</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Mohawk activist. Fought to restore Indigenous women's status under Indian Act.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Tier 2 – Modern</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
           <t>Pierre Elliott Trudeau</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>1919–2000</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Monument: +1 Culture · Courthouse: +1 Mandate</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>15th PM, Charter of Rights architect, 'Just Society.' Monument and courthouse.</t>
         </is>
@@ -5194,7 +5245,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5586,7 +5637,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>DOCTRINE MODS</t>
         </is>
@@ -5657,7 +5708,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>AXIS MODS — REASON ↔ PROVIDENCE</t>
         </is>
@@ -6378,7 +6429,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>VICE PRESIDENT RELATIONSHIP ARC  ·  [COMMANDER_NAME] is the player-chosen VP</t>
         </is>
@@ -6749,32 +6800,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>UK_DECLARATION_01</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>CROWN DECLARES WAR ON THE CONTINENTAL REPUBLIC</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Fires on UK declaration</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Opens Canadian alliance tree; changes diplomatic options</t>
         </is>
@@ -6823,32 +6874,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>CAN_PENOIT_01</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>MARC PENOIT OF THE HABITANTS RECEIVES THE MESSAGE</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Req: can_contact flag</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>→ CAN_CLEARWATER_01; introduces Penoit as CA liaison</t>
         </is>
@@ -6897,32 +6948,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>JOINT OPERATIONS: CONTINENTAL AND CANADIAN FORCES COORDINATE</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Req: CAN_CLEARWATER_01</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>→ CAN_SUMMIT_01; first military cooperation event</t>
         </is>
@@ -6971,32 +7022,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>CAN_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>CONTINENTAL-CANADIAN ALLIANCE FORMALIZED</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Req: CAN_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Sets can_allied flag; major diplomatic milestone</t>
         </is>
@@ -7045,32 +7096,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>THE CANADIAN ELECTION: A CONTINENTAL ALLY WINS</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Req: can_allied</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Bonus loyalty or resource gift; diplomatic goodwill event</t>
         </is>
@@ -7119,32 +7170,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>USA_CALL_01</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>A DISPATCH FROM WASHINGTON — THE AMERICANS WANT TO TALK</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Root (turn 8+, req: uk_buildup_known)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Sets usa_contact flag; gates USA_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>BTN1: Hear them out (→ USA_SUMMIT_01) · BTN2: Decline (sets usa_rejected → CA_ALONE_01)</t>
         </is>
@@ -7193,32 +7244,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>USA_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>THE CANADIAN-CONTINENTAL ACCORD IS SIGNED</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Branch (req: usa_summit_complete)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Sets ca_allied flag; mirrors CAN_ALLIANCE_SIGNED from USA side</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Narrative resolution; alliance milestone event</t>
         </is>
@@ -7274,7 +7325,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE WENDIGO</t>
         </is>
@@ -7392,7 +7443,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE LOUP-GAROU</t>
         </is>
@@ -7510,7 +7561,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LES FEUX FOLLETS</t>
         </is>
@@ -7628,7 +7679,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — MISHEPESHU</t>
         </is>
@@ -7746,7 +7797,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CORRIVEAU</t>
         </is>
@@ -7864,7 +7915,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE CARCAJOU</t>
         </is>
@@ -7982,7 +8033,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CHASSE-GALERIE</t>
         </is>
@@ -8100,7 +8151,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE GOUGOU</t>
         </is>
@@ -8218,7 +8269,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — MOTHMAN</t>
         </is>
@@ -8336,7 +8387,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — JERSEY DEVIL</t>
         </is>
@@ -8454,7 +8505,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — HEADLESS HORSEMAN</t>
         </is>
@@ -8572,7 +8623,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — GOATMAN</t>
         </is>
@@ -8727,7 +8778,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — BELL WITCH</t>
         </is>
@@ -8882,7 +8933,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — OLD IRONSIDES</t>
         </is>
@@ -9000,7 +9051,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — AGENT 355</t>
         </is>
@@ -9118,7 +9169,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — LINCOLN'S GHOST</t>
         </is>
@@ -9236,7 +9287,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="inlineStr">
+      <c r="A85" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — WOOD BOOGER</t>
         </is>
@@ -9354,7 +9405,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — PAMOLA</t>
         </is>
@@ -9472,7 +9523,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="inlineStr">
+      <c r="A93" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — SNALLYGASTER</t>
         </is>
@@ -9590,7 +9641,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+      <c r="A97" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — BLACK DOG</t>
         </is>
@@ -9708,7 +9759,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="A101" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — MERCY BROWN</t>
         </is>
@@ -9826,7 +9877,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="17" t="inlineStr">
+      <c r="A105" s="18" t="inlineStr">
         <is>
           <t>USA PROTECTOR — CHAMP</t>
         </is>

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FACTIONS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LAWS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DOCTRINES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ICONS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BELIEF MODS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="GOVERNORS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VP ARC" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CA EVENTS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACTIONS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LAWS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOCTRINES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICONS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BELIEF MODS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOVERNORS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VP ARC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CA EVENTS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>AXIS MODS — REASON ↔ PROVIDENCE</t>
+          <t>AXIS MODS — ROMANTIC ↔ RATIONAL</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Axis — Providence III (churchLevel +3)</t>
+          <t>Axis — Rational III (churchLevel +3)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>A nation deeply committed to Providence digs in and holds. Faith becomes fortification. The Republic will not be moved from ground it has consecrated.</t>
+          <t>A republic of pure social contract digs in and holds — system and statute become fortification. It will not be moved from ground it has lawfully organized.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Axis — Reason III (churchLevel −3)</t>
+          <t>Axis — Romantic III (churchLevel −3)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>An Enlightened Republic trains marksmen, not martyrs. Precision over prayer. The rifle doesn't need divine blessing — it needs a steady hand and a clear eye.</t>
+          <t>A republic of heroes makes legends of its marksmen. Every shot carries the memory of a folk hero — precision passed down as myth, the steady hand made immortal.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">

--- a/flavordoc.xlsx
+++ b/flavordoc.xlsx
@@ -87,7 +87,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -151,6 +151,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001A4D3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002E4057"/>
       </patternFill>
     </fill>
@@ -201,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,13 +253,16 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -775,14 +783,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -5259,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5534,36 +5542,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>CANADIAN ICON MODS</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>PRESIDENTIAL AURAS — UALANI'S GIFT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Beaverdams Dispatch</t>
+          <t>Beautiful Flower</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Icon — Laura Secord</t>
+          <t>Intro — Ualani's Inauguration Gift</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>commanderMod</t>
+          <t>ualaniAura</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+3 Defense per Level in tiles with Barracks or Fortress</t>
+          <t>+3 Defense to all friendly units adjacent to Ualani</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison was ready. The Americans surrendered.</t>
+          <t>They called her ka pua nani — the beautiful flower — and a flower is a thing soldiers will stand in front of. Where Ualani plants herself, the line does not break.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -5575,83 +5583,83 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Batoche's Stand</t>
+          <t>Executive Enforcer</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Icon — Louis Riel</t>
+          <t>Intro — Ualani's Inauguration Gift</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>infantryMod (terrainMod: Woods)</t>
+          <t>ualaniAura</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain (temp)</t>
+          <t>+3 Attack to all friendly units adjacent to Ualani</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>May 1885: The Métis held Batoche for four days with hunting rifles, kitchen knives, and nails fired from improvised guns. Against a professional army. They lasted longer than anyone expected.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+          <t>The other face of President Carlisle: not a symbol to be shielded but a will to be obeyed. When she takes the field, hesitation burns off the advance — and the Republic's enemies learn what 'ʻOnipaʻa' costs them.</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Peacekeeping Mandate</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Icon — Roméo Dallaire</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>CANADIAN ICON MODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Beaverdams Dispatch</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Icon — Laura Secord</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>commanderMod</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>+2 Defense per Level (temp — rout system pending full pass)</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1994: Dallaire commanded UNAMIR in Rwanda with 2,500 troops and no mandate to stop a genocide. He stayed anyway. His testimony shaped every peacekeeping doctrine that followed.</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>DOCTRINE MODS</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>+3 Defense per Level in tiles with Barracks or Fortress</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>June 1813: Secord walked 20 miles through American-occupied territory to warn Lt. FitzGibbon of an approaching attack. The garrison was ready. The Americans surrendered.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Woodsman</t>
+          <t>Batoche's Stand</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Doctrine — Inland Maritime Expertise / National Parks Act</t>
+          <t>Icon — Louis Riel</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -5661,29 +5669,29 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain (temp)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>The wilderness is not hostile to those who know it. Frontier rangers, trappers, and scouts treat the forest as cover, not obstacle.</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>May 1885: The Métis held Batoche for four days with hunting rifles, kitchen knives, and nails fired from improvised guns. Against a professional army. They lasted longer than anyone expected.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Peacekeeping Mandate</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Doctrine — Defense Production Act / War Measures Act</t>
+          <t>Icon — Roméo Dallaire</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5693,51 +5701,51 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>+4 Attack per Level on first engagement in a fresh tile</t>
+          <t>+2 Defense per Level (temp — rout system pending full pass)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Industrial war footing means the army that strikes first has superior materiel. The first charge carries the advantage of preparation.</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>1994: Dallaire commanded UNAMIR in Rwanda with 2,500 troops and no mandate to stop a genocide. He stayed anyway. His testimony shaped every peacekeeping doctrine that followed.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>AXIS MODS — ROMANTIC ↔ RATIONAL</t>
+          <t>DOCTRINE MODS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Entrenched</t>
+          <t>Woodsman</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Axis — Rational III (churchLevel +3)</t>
+          <t>Doctrine — Inland Maritime Expertise / National Parks Act</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>commanderMod (entrenchMod)</t>
+          <t>infantryMod (terrainMod: Woods)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>+5 Defense after 3 stationary turns; lost on movement</t>
+          <t>+2 Attack, +2 Defense per Level in Woods terrain</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>A republic of pure social contract digs in and holds — system and statute become fortification. It will not be moved from ground it has lawfully organized.</t>
+          <t>The wilderness is not hostile to those who know it. Frontier rangers, trappers, and scouts treat the forest as cover, not obstacle.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5749,41 +5757,113 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Vanguard</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Doctrine — Defense Production Act / War Measures Act</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>+4 Attack per Level on first engagement in a fresh tile</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Industrial war footing means the army that strikes first has superior materiel. The first charge carries the advantage of preparation.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>AXIS MODS — ROMANTIC ↔ RATIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Entrenched</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Axis — Rational III (churchLevel +3)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>commanderMod (entrenchMod)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>+5 Defense after 3 stationary turns; lost on movement</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>A republic of pure social contract digs in and holds — system and statute become fortification. It will not be moved from ground it has lawfully organized.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>Sharpshooter</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Axis — Romantic III (churchLevel −3)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>rangedMod</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Ranged attacks ignore 2 enemy Defense per Level</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>A republic of heroes makes legends of its marksmen. Every shot carries the memory of a folk hero — precision passed down as myth, the steady hand made immortal.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>FIRST PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6429,7 +6509,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>VICE PRESIDENT RELATIONSHIP ARC  ·  [COMMANDER_NAME] is the player-chosen VP</t>
         </is>
@@ -6800,32 +6880,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>UK_DECLARATION_01</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>CROWN DECLARES WAR ON THE CONTINENTAL REPUBLIC</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Fires on UK declaration</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Opens Canadian alliance tree; changes diplomatic options</t>
         </is>
@@ -6874,32 +6954,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>CAN_PENOIT_01</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>MARC PENOIT OF THE HABITANTS RECEIVES THE MESSAGE</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>Req: can_contact flag</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>→ CAN_CLEARWATER_01; introduces Penoit as CA liaison</t>
         </is>
@@ -6948,32 +7028,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>JOINT OPERATIONS: CONTINENTAL AND CANADIAN FORCES COORDINATE</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Req: CAN_CLEARWATER_01</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>→ CAN_SUMMIT_01; first military cooperation event</t>
         </is>
@@ -7022,32 +7102,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>CAN_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>CONTINENTAL-CANADIAN ALLIANCE FORMALIZED</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Req: CAN_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>Sets can_allied flag; major diplomatic milestone</t>
         </is>
@@ -7096,32 +7176,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>THE CANADIAN ELECTION: A CONTINENTAL ALLY WINS</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>Req: can_allied</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>Bonus loyalty or resource gift; diplomatic goodwill event</t>
         </is>
@@ -7170,32 +7250,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>USA_CALL_01</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>A DISPATCH FROM WASHINGTON — THE AMERICANS WANT TO TALK</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Root (turn 8+, req: uk_buildup_known)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>Sets usa_contact flag; gates USA_SUMMIT_01</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>BTN1: Hear them out (→ USA_SUMMIT_01) · BTN2: Decline (sets usa_rejected → CA_ALONE_01)</t>
         </is>
@@ -7244,32 +7324,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>USA Alliance Arc</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>USA_ALLIANCE_SIGNED</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>THE CANADIAN-CONTINENTAL ACCORD IS SIGNED</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Branch (req: usa_summit_complete)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Sets ca_allied flag; mirrors CAN_ALLIANCE_SIGNED from USA side</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Narrative resolution; alliance milestone event</t>
         </is>
@@ -7325,7 +7405,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE WENDIGO</t>
         </is>
@@ -7443,7 +7523,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE LOUP-GAROU</t>
         </is>
@@ -7561,7 +7641,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LES FEUX FOLLETS</t>
         </is>
@@ -7679,7 +7759,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — MISHEPESHU</t>
         </is>
@@ -7797,7 +7877,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CORRIVEAU</t>
         </is>
@@ -7915,7 +7995,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE CARCAJOU</t>
         </is>
@@ -8033,7 +8113,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LA CHASSE-GALERIE</t>
         </is>
@@ -8151,7 +8231,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>CA PROTECTOR — LE GOUGOU</t>
         </is>
@@ -8269,7 +8349,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — MOTHMAN</t>
         </is>
@@ -8387,7 +8467,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — JERSEY DEVIL</t>
         </is>
@@ -8505,7 +8585,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — HEADLESS HORSEMAN</t>
         </is>
@@ -8623,7 +8703,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — GOATMAN</t>
         </is>
@@ -8778,7 +8858,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — BELL WITCH</t>
         </is>
@@ -8933,7 +9013,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — OLD IRONSIDES</t>
         </is>
@@ -9051,7 +9131,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — AGENT 355</t>
         </is>
@@ -9169,7 +9249,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — LINCOLN'S GHOST</t>
         </is>
@@ -9287,7 +9367,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — WOOD BOOGER</t>
         </is>
@@ -9405,7 +9485,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — PAMOLA</t>
         </is>
@@ -9523,7 +9603,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="18" t="inlineStr">
+      <c r="A93" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — SNALLYGASTER</t>
         </is>
@@ -9641,7 +9721,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="18" t="inlineStr">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — BLACK DOG</t>
         </is>
@@ -9759,7 +9839,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="18" t="inlineStr">
+      <c r="A101" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — MERCY BROWN</t>
         </is>
@@ -9877,7 +9957,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>USA PROTECTOR — CHAMP</t>
         </is>
